--- a/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ4"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -962,8 +962,212 @@
       <c r="AI4" s="2" t="inlineStr"/>
       <c r="AJ4" s="2" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>b451a773d4b34f38</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0.599195</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0.01936306722689085</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:04.678326Z</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>eb1b042c54994532</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0.662883</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.022595230215827322</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:10.799851Z</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ4"/>
+  <autoFilter ref="A1:AJ6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1166,8 +1166,518 @@
       <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>cf6e023e08ec496c</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0.599195</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0.01936306722689085</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:26.813178Z</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>8e46df262a644c7c</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.662883</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0.022595230215827322</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:30.646895Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>58f346ac75034f4a</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>69263</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.68024</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.020376054421768597</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:19.829844Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>99e87bb91f874da6</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.599198</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.019366067226890826</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:25.545768Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>e2a820ac03c74ff0</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.663025</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.022737230215827298</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:29.527479Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ6"/>
+  <autoFilter ref="A1:AJ11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1676,8 +1676,212 @@
       <c r="AI11" s="2" t="inlineStr"/>
       <c r="AJ11" s="2" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ba534c70fe1f411c</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.599199</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.019367067226890855</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:31.821007Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>30e1979094984b9b</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.663041</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.022753230215827314</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:36.924167Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ11"/>
+  <autoFilter ref="A1:AJ13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ13"/>
+  <dimension ref="A1:AJ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1880,8 +1880,314 @@
       <c r="AI13" s="2" t="inlineStr"/>
       <c r="AJ13" s="2" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>c8d6199850d44408</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.599199</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.019367067226890855</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:46.352076Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>5b8cd56a8de840fd</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>67514</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.639896</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0.02012413688212933</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:48.789246Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>72bd529883d441d2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.663041</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>0.022753230215827314</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:51.418739Z</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ13"/>
+  <autoFilter ref="A1:AJ16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2186,8 +2186,314 @@
       <c r="AI16" s="2" t="inlineStr"/>
       <c r="AJ16" s="2" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>72b040bfb83342ea</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0.599274</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0.01944206722689079</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:35.118991Z</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>6950153379534f9d</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>67514</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.640004</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>0.020232136882129326</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:37.624827Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>3658806e64bd47e9</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.663166</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0.022878230215827355</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:40.237935Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ16"/>
+  <autoFilter ref="A1:AJ19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AJ80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2492,8 +2492,6250 @@
       <c r="AI19" s="2" t="inlineStr"/>
       <c r="AJ19" s="2" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>89e9cf2fc75b4aa1</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>e4232d2f4ef51c47f2dc842e10597bebb70952e9ec25e243147604e0ae4edf92</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.663283</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0.022995230215827278</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:50:12.693993Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>b3904199c894447c</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>051e3df946405e100b8250180227c6a35bf6c62b302c77c1d1682b65da349694</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.663283</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0.022995230215827278</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:31:47.216808Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>32ba3dd540964624</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>fdeba1668c2500d71094a9d36677273c1f10a89d3cac97cf2e8cf2fbd0efe7b0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.662876</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0.01252634965034971</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:16:42.836459Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>69012f80ee3146fd</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>8ecc1c8e011b0039985213cb24b0dd9b7c49154adcc57e89a59cc5370175e29a</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.662876</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0.022588230215827343</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:46:53.507386Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>7e235e4eae484888</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>8ecc1c8e011b0039985213cb24b0dd9b7c49154adcc57e89a59cc5370175e29a</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>70374</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.691763</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>0.1612465680751174</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:46:54.580347Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>13343d46cfb14958</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>caeb7a72f44ac75f550b7c2ea44098ab320888b86befea14b64dcc781c6dce82</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.662876</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.022588230215827343</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:19:13.559149Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>d3f01cc590c84b26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>caeb7a72f44ac75f550b7c2ea44098ab320888b86befea14b64dcc781c6dce82</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>70374</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.691765</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>0.13229363436123343</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:19:15.799577Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>4f151d8140ec4fd0</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>caeb7a72f44ac75f550b7c2ea44098ab320888b86befea14b64dcc781c6dce82</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>69549</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.63329</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>0.09411949308755763</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:19:21.464029Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>7184f61e64de4dd2</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>caeb7a72f44ac75f550b7c2ea44098ab320888b86befea14b64dcc781c6dce82</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.550886</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>0.11035736563876652</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:19:24.077308Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>b8b31d7700784949</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>7d07e567fea5bd3738b3dbc4e35eb295221f9dc89d0247f1cc7d87e37942825c</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.662876</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>0.03324637037037048</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:31:22.204074Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>47b318aafa6e4b54</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>7d07e567fea5bd3738b3dbc4e35eb295221f9dc89d0247f1cc7d87e37942825c</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>70374</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.691765</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.13229363436123343</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:31:24.336217Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>db470deab7e44ec7</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>7d07e567fea5bd3738b3dbc4e35eb295221f9dc89d0247f1cc7d87e37942825c</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>68293</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.617622</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>0.017621999999999916</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:31:24.822120Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>3a59d5cd3824452b</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>7d07e567fea5bd3738b3dbc4e35eb295221f9dc89d0247f1cc7d87e37942825c</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>69549</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0.63329</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>0.09411949308755763</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:31:30.277240Z</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>5e7364477b5a46ca</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>7d07e567fea5bd3738b3dbc4e35eb295221f9dc89d0247f1cc7d87e37942825c</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0.550886</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>0.11035736563876652</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:31:32.986727Z</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>62bca48cfb3d446f</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>a67b482e0cc299818c9d6a6183162092d6b3cbeea4f974054606da1c44c3bd99</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>67514</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0.639821</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0.030445999999999973</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:14:38.370048Z</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>0.610000</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0.000625</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0.9615</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:27:35.742840Z</t>
+        </is>
+      </c>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>8a07b4bba9a54f02</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>a67b482e0cc299818c9d6a6183162092d6b3cbeea4f974054606da1c44c3bd99</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0.662876</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0.03324637037037048</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:14:43.561547Z</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>85588c41e6e649e4</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>a67b482e0cc299818c9d6a6183162092d6b3cbeea4f974054606da1c44c3bd99</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>70374</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0.691765</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>0.13229363436123343</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:14:45.054907Z</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>c518dfebe3824b2f</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>a67b482e0cc299818c9d6a6183162092d6b3cbeea4f974054606da1c44c3bd99</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>68293</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0.617622</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0.017621999999999916</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:14:46.564518Z</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>3ba16b6b3b4242b6</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>a67b482e0cc299818c9d6a6183162092d6b3cbeea4f974054606da1c44c3bd99</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>69549</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0.63329</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>0.09411949308755763</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:14:50.162650Z</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>9a7f3e38ac96411d</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>a67b482e0cc299818c9d6a6183162092d6b3cbeea4f974054606da1c44c3bd99</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>0.550886</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>0.11035736563876652</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:14:53.316129Z</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>4ed5d0f5b32c42ff</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>cf8bba36d77af68a9833ecd35cfd7fb79b0070036fcffef471b5ca12e7c93451</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0.662853</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0.033223370370370486</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:20.072938Z</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>3fa74665915640d0</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>cf8bba36d77af68a9833ecd35cfd7fb79b0070036fcffef471b5ca12e7c93451</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>70374</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0.691814</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0.1323426343612335</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:20.634568Z</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>8915970da404440c</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>cf8bba36d77af68a9833ecd35cfd7fb79b0070036fcffef471b5ca12e7c93451</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>68293</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>0.617805</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0.01780499999999996</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:23.104635Z</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>9bc3f4a5b6954d82</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>cf8bba36d77af68a9833ecd35cfd7fb79b0070036fcffef471b5ca12e7c93451</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>69549</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0.63326</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0.09408949308755765</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:27.805140Z</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>699c892ee0604f84</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>cf8bba36d77af68a9833ecd35cfd7fb79b0070036fcffef471b5ca12e7c93451</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0.550937</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0.11040836563876655</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:29.513762Z</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>09814b21e27f4c4f</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>9788ee890acda4c62d77d79ea2b1f172c9d4d87af2458e9365985663c60a50c8</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>0.662853</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>0.033223370370370486</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:47.351382Z</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>63887e6208e943db</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>9788ee890acda4c62d77d79ea2b1f172c9d4d87af2458e9365985663c60a50c8</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>70374</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0.691814</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>0.1323426343612335</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:47.844788Z</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
+      <c r="AJ46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>9d1de3ad37a74b92</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>9788ee890acda4c62d77d79ea2b1f172c9d4d87af2458e9365985663c60a50c8</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>68293</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0.617805</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0.01780499999999996</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:50.138307Z</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>94b8129dda7e4041</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>9788ee890acda4c62d77d79ea2b1f172c9d4d87af2458e9365985663c60a50c8</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>69549</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0.63326</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0.09408949308755765</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:55.154803Z</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>31897a9008f543ca</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>9788ee890acda4c62d77d79ea2b1f172c9d4d87af2458e9365985663c60a50c8</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0.550937</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0.11040836563876655</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:56.799251Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>996002a8ee4f46e8</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>f4f3549fbe9f095af12acefc96610fcfd4a51f4257b8523d5f8648d7efb51e9b</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>70374</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0.691757</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>0.13228563436123342</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:35.838085Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>ce11e9b923874284</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>f4f3549fbe9f095af12acefc96610fcfd4a51f4257b8523d5f8648d7efb51e9b</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>69549</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>0.650663</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0.1114924930875576</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:43.570244Z</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>ba32c492cc4a4de4</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>f4f3549fbe9f095af12acefc96610fcfd4a51f4257b8523d5f8648d7efb51e9b</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>0.551038</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>0.11050936563876657</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:45.362921Z</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="2" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>aec4e76081014bf7</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>c66a6812ab11fc0dd1f6ac648df14199783726b2399c60a0fd85c70b95d8390a</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>70374</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>0.691798</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>0.12098254935622321</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:18.773063Z</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr"/>
+      <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AG53" s="2" t="inlineStr"/>
+      <c r="AH53" s="2" t="inlineStr"/>
+      <c r="AI53" s="2" t="inlineStr"/>
+      <c r="AJ53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>cdda8b4799f14145</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>c66a6812ab11fc0dd1f6ac648df14199783726b2399c60a0fd85c70b95d8390a</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>70532</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>0.630684</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>0.030683999999999934</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:22.911575Z</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>29dda2d7e6144e78</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>c66a6812ab11fc0dd1f6ac648df14199783726b2399c60a0fd85c70b95d8390a</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>69549</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>0.650234</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>0.11106349308755759</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:23.975573Z</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr"/>
+      <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AG55" s="2" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AI55" s="2" t="inlineStr"/>
+      <c r="AJ55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>99079c56f87d4b3e</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>c66a6812ab11fc0dd1f6ac648df14199783726b2399c60a0fd85c70b95d8390a</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>70689</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0.685765</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>0.14659449308755756</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:25.735528Z</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr"/>
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AJ56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>bfe50913ab7243ef</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>c66a6812ab11fc0dd1f6ac648df14199783726b2399c60a0fd85c70b95d8390a</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>0.551354</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>0.1009035495495495</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:28.443538Z</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>83a770029e984bd9</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>3467f28bd46afdbb5a0d864402eda1a270a0f9a7b398be1585c42b2d936704a4</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>70532</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>0.63086</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>0.030859999999999888</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:30:59.712659Z</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="2" t="inlineStr"/>
+      <c r="AH58" s="2" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>06f800c8565f4acf</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>3467f28bd46afdbb5a0d864402eda1a270a0f9a7b398be1585c42b2d936704a4</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>69549</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>0.650235</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>0.11106449308755761</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:31:01.999214Z</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AF59" s="2" t="inlineStr"/>
+      <c r="AG59" s="2" t="inlineStr"/>
+      <c r="AH59" s="2" t="inlineStr"/>
+      <c r="AI59" s="2" t="inlineStr"/>
+      <c r="AJ59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>694d0868f15a4dbc</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>3467f28bd46afdbb5a0d864402eda1a270a0f9a7b398be1585c42b2d936704a4</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>70689</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>0.685963</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>0.1467924930875576</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:31:03.002645Z</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr"/>
+      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr"/>
+      <c r="AG60" s="2" t="inlineStr"/>
+      <c r="AH60" s="2" t="inlineStr"/>
+      <c r="AI60" s="2" t="inlineStr"/>
+      <c r="AJ60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>53afa295057e4174</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>3467f28bd46afdbb5a0d864402eda1a270a0f9a7b398be1585c42b2d936704a4</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>0.551488</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>0.10103754954954947</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:31:05.271048Z</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr"/>
+      <c r="AE61" s="2" t="inlineStr"/>
+      <c r="AF61" s="2" t="inlineStr"/>
+      <c r="AG61" s="2" t="inlineStr"/>
+      <c r="AH61" s="2" t="inlineStr"/>
+      <c r="AI61" s="2" t="inlineStr"/>
+      <c r="AJ61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>da5a75272a4f492e</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>ac6ceef0c5562ec6cc6578a41665f813f640606150062d7159d6470d651252c3</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>70532</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>0.630846</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>0.03084599999999993</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:51:15.415069Z</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr"/>
+      <c r="AE62" s="2" t="inlineStr"/>
+      <c r="AF62" s="2" t="inlineStr"/>
+      <c r="AG62" s="2" t="inlineStr"/>
+      <c r="AH62" s="2" t="inlineStr"/>
+      <c r="AI62" s="2" t="inlineStr"/>
+      <c r="AJ62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>ce7376570a054afe</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>ac6ceef0c5562ec6cc6578a41665f813f640606150062d7159d6470d651252c3</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>69549</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>0.65036</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>0.11118949308755766</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:51:17.322134Z</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr"/>
+      <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="2" t="inlineStr"/>
+      <c r="AG63" s="2" t="inlineStr"/>
+      <c r="AH63" s="2" t="inlineStr"/>
+      <c r="AI63" s="2" t="inlineStr"/>
+      <c r="AJ63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>501d627f82324632</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>ac6ceef0c5562ec6cc6578a41665f813f640606150062d7159d6470d651252c3</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>70689</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>0.685971</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>0.1468004930875576</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:51:17.777471Z</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr"/>
+      <c r="AE64" s="2" t="inlineStr"/>
+      <c r="AF64" s="2" t="inlineStr"/>
+      <c r="AG64" s="2" t="inlineStr"/>
+      <c r="AH64" s="2" t="inlineStr"/>
+      <c r="AI64" s="2" t="inlineStr"/>
+      <c r="AJ64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>335c6bd8ffb94b4d</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>ac6ceef0c5562ec6cc6578a41665f813f640606150062d7159d6470d651252c3</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>0.551438</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>0.10098754954954947</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:51:19.950081Z</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr"/>
+      <c r="AE65" s="2" t="inlineStr"/>
+      <c r="AF65" s="2" t="inlineStr"/>
+      <c r="AG65" s="2" t="inlineStr"/>
+      <c r="AH65" s="2" t="inlineStr"/>
+      <c r="AI65" s="2" t="inlineStr"/>
+      <c r="AJ65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>3507c279b3eb4e2d</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>c35f4cde86576db9aef02f14800a622a7aeabf3f364ac4b428aed69c2c8f4d15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>70532</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>0.630798</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>0.03079799999999988</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:08:43.813161Z</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr"/>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr"/>
+      <c r="AE66" s="2" t="inlineStr"/>
+      <c r="AF66" s="2" t="inlineStr"/>
+      <c r="AG66" s="2" t="inlineStr"/>
+      <c r="AH66" s="2" t="inlineStr"/>
+      <c r="AI66" s="2" t="inlineStr"/>
+      <c r="AJ66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>53a3068218e14e93</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>c35f4cde86576db9aef02f14800a622a7aeabf3f364ac4b428aed69c2c8f4d15</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>69549</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>0.650343</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>0.11117249308755761</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:08:45.810896Z</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr"/>
+      <c r="AE67" s="2" t="inlineStr"/>
+      <c r="AF67" s="2" t="inlineStr"/>
+      <c r="AG67" s="2" t="inlineStr"/>
+      <c r="AH67" s="2" t="inlineStr"/>
+      <c r="AI67" s="2" t="inlineStr"/>
+      <c r="AJ67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>8e27d201c8774097</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>c35f4cde86576db9aef02f14800a622a7aeabf3f364ac4b428aed69c2c8f4d15</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>70689</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>0.685916</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>0.14674549308755758</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:08:46.839717Z</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr"/>
+      <c r="W68" s="2" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr"/>
+      <c r="AA68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr"/>
+      <c r="AE68" s="2" t="inlineStr"/>
+      <c r="AF68" s="2" t="inlineStr"/>
+      <c r="AG68" s="2" t="inlineStr"/>
+      <c r="AH68" s="2" t="inlineStr"/>
+      <c r="AI68" s="2" t="inlineStr"/>
+      <c r="AJ68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>3302bbc0c45c4b3c</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>c35f4cde86576db9aef02f14800a622a7aeabf3f364ac4b428aed69c2c8f4d15</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>0.551403</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>0.10095254954954946</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:08:49.211679Z</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr"/>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr"/>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr"/>
+      <c r="AE69" s="2" t="inlineStr"/>
+      <c r="AF69" s="2" t="inlineStr"/>
+      <c r="AG69" s="2" t="inlineStr"/>
+      <c r="AH69" s="2" t="inlineStr"/>
+      <c r="AI69" s="2" t="inlineStr"/>
+      <c r="AJ69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>5ab66ca1aba04003</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>49e72bc47e8b746259057b18a0727b3402ae02f53069edfae5b6532757438c2c</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>70532</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>0.630438</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>0.030437999999999965</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:54:46.268393Z</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr"/>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr"/>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr"/>
+      <c r="AE70" s="2" t="inlineStr"/>
+      <c r="AF70" s="2" t="inlineStr"/>
+      <c r="AG70" s="2" t="inlineStr"/>
+      <c r="AH70" s="2" t="inlineStr"/>
+      <c r="AI70" s="2" t="inlineStr"/>
+      <c r="AJ70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>9b01fcef9cc1410b</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>49e72bc47e8b746259057b18a0727b3402ae02f53069edfae5b6532757438c2c</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>69549</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>0.650251</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>0.060087065573770526</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:54:48.457020Z</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr"/>
+      <c r="AE71" s="2" t="inlineStr"/>
+      <c r="AF71" s="2" t="inlineStr"/>
+      <c r="AG71" s="2" t="inlineStr"/>
+      <c r="AH71" s="2" t="inlineStr"/>
+      <c r="AI71" s="2" t="inlineStr"/>
+      <c r="AJ71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>a6f5f31ae54243a7</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>49e72bc47e8b746259057b18a0727b3402ae02f53069edfae5b6532757438c2c</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>70689</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>0.685593</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>0.015626003300330038</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:54:48.946549Z</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr"/>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr"/>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr"/>
+      <c r="AE72" s="2" t="inlineStr"/>
+      <c r="AF72" s="2" t="inlineStr"/>
+      <c r="AG72" s="2" t="inlineStr"/>
+      <c r="AH72" s="2" t="inlineStr"/>
+      <c r="AI72" s="2" t="inlineStr"/>
+      <c r="AJ72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>83b426a2e05047ee</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>49e72bc47e8b746259057b18a0727b3402ae02f53069edfae5b6532757438c2c</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>0.551138</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>0.1006875495495495</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:54:51.669161Z</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr"/>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr"/>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr"/>
+      <c r="AE73" s="2" t="inlineStr"/>
+      <c r="AF73" s="2" t="inlineStr"/>
+      <c r="AG73" s="2" t="inlineStr"/>
+      <c r="AH73" s="2" t="inlineStr"/>
+      <c r="AI73" s="2" t="inlineStr"/>
+      <c r="AJ73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>a0fe3529d943496b</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>2395c0bc2d118cb68697847c5524bbbcdf615284bfa6589bd672b76fe7c39141</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>0.551005</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>0.09017550691244236</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:57:53.522811Z</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr"/>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr"/>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr"/>
+      <c r="AE74" s="2" t="inlineStr"/>
+      <c r="AF74" s="2" t="inlineStr"/>
+      <c r="AG74" s="2" t="inlineStr"/>
+      <c r="AH74" s="2" t="inlineStr"/>
+      <c r="AI74" s="2" t="inlineStr"/>
+      <c r="AJ74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>3f8f7e51f3f64830</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>2395c0bc2d118cb68697847c5524bbbcdf615284bfa6589bd672b76fe7c39141</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>71280</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>0.640951</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>0.03157600000000005</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:57:55.103444Z</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr"/>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr"/>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr"/>
+      <c r="AE75" s="2" t="inlineStr"/>
+      <c r="AF75" s="2" t="inlineStr"/>
+      <c r="AG75" s="2" t="inlineStr"/>
+      <c r="AH75" s="2" t="inlineStr"/>
+      <c r="AI75" s="2" t="inlineStr"/>
+      <c r="AJ75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>ec1d23d4fd8f4533</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>0.551006</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>0.09017650691244239</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:44.822978Z</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr"/>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr"/>
+      <c r="AE76" s="2" t="inlineStr"/>
+      <c r="AF76" s="2" t="inlineStr"/>
+      <c r="AG76" s="2" t="inlineStr"/>
+      <c r="AH76" s="2" t="inlineStr"/>
+      <c r="AI76" s="2" t="inlineStr"/>
+      <c r="AJ76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ccf96e11ad2d4c34</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>71501</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>0.691599</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>0.11176706722689078</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:45.360175Z</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr"/>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr"/>
+      <c r="AE77" s="2" t="inlineStr"/>
+      <c r="AF77" s="2" t="inlineStr"/>
+      <c r="AG77" s="2" t="inlineStr"/>
+      <c r="AH77" s="2" t="inlineStr"/>
+      <c r="AI77" s="2" t="inlineStr"/>
+      <c r="AJ77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>fbf3c2a31f424364</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>71385</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>0.576412</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>0.06660807843137262</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:54.911657Z</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr"/>
+      <c r="W78" s="2" t="inlineStr"/>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr"/>
+      <c r="AA78" s="2" t="inlineStr"/>
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr"/>
+      <c r="AE78" s="2" t="inlineStr"/>
+      <c r="AF78" s="2" t="inlineStr"/>
+      <c r="AG78" s="2" t="inlineStr"/>
+      <c r="AH78" s="2" t="inlineStr"/>
+      <c r="AI78" s="2" t="inlineStr"/>
+      <c r="AJ78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>1a7ff66b86254217</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>71390</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>0.598969</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>0.08916507843137256</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:57.015430Z</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr"/>
+      <c r="W79" s="2" t="inlineStr"/>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr"/>
+      <c r="AA79" s="2" t="inlineStr"/>
+      <c r="AB79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr"/>
+      <c r="AE79" s="2" t="inlineStr"/>
+      <c r="AF79" s="2" t="inlineStr"/>
+      <c r="AG79" s="2" t="inlineStr"/>
+      <c r="AH79" s="2" t="inlineStr"/>
+      <c r="AI79" s="2" t="inlineStr"/>
+      <c r="AJ79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>017fb4c4fb6d4759</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>15c4c90af7c7e70d96e71add7b9cc8fbed98352fcea88c83a1a27ed966f78c49</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>0.67501</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>0.05523813688212931</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T04:00:07.463015Z</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr"/>
+      <c r="W80" s="2" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr"/>
+      <c r="Z80" s="2" t="inlineStr"/>
+      <c r="AA80" s="2" t="inlineStr"/>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr"/>
+      <c r="AE80" s="2" t="inlineStr"/>
+      <c r="AF80" s="2" t="inlineStr"/>
+      <c r="AG80" s="2" t="inlineStr"/>
+      <c r="AH80" s="2" t="inlineStr"/>
+      <c r="AI80" s="2" t="inlineStr"/>
+      <c r="AJ80" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ19"/>
+  <autoFilter ref="A1:AJ80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ80"/>
+  <dimension ref="A1:AJ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8734,8 +8734,1436 @@
       <c r="AI80" s="2" t="inlineStr"/>
       <c r="AJ80" s="2" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>74c1ed1514654a18</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>0.551011</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>0.0608149215686275</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:23.843519Z</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="2" t="inlineStr"/>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr"/>
+      <c r="Z81" s="2" t="inlineStr"/>
+      <c r="AA81" s="2" t="inlineStr"/>
+      <c r="AB81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr"/>
+      <c r="AE81" s="2" t="inlineStr"/>
+      <c r="AF81" s="2" t="inlineStr"/>
+      <c r="AG81" s="2" t="inlineStr"/>
+      <c r="AH81" s="2" t="inlineStr"/>
+      <c r="AI81" s="2" t="inlineStr"/>
+      <c r="AJ81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>fa08d43d714f4430</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>71501</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>0.691594</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>0.11176206722689086</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:24.962601Z</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="2" t="inlineStr"/>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr"/>
+      <c r="Z82" s="2" t="inlineStr"/>
+      <c r="AA82" s="2" t="inlineStr"/>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr"/>
+      <c r="AE82" s="2" t="inlineStr"/>
+      <c r="AF82" s="2" t="inlineStr"/>
+      <c r="AG82" s="2" t="inlineStr"/>
+      <c r="AH82" s="2" t="inlineStr"/>
+      <c r="AI82" s="2" t="inlineStr"/>
+      <c r="AJ82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>d41a8c6d757a4cc7</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>0.698419</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>0.1679025680751174</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:39.377337Z</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr"/>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr"/>
+      <c r="Z83" s="2" t="inlineStr"/>
+      <c r="AA83" s="2" t="inlineStr"/>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr"/>
+      <c r="AE83" s="2" t="inlineStr"/>
+      <c r="AF83" s="2" t="inlineStr"/>
+      <c r="AG83" s="2" t="inlineStr"/>
+      <c r="AH83" s="2" t="inlineStr"/>
+      <c r="AI83" s="2" t="inlineStr"/>
+      <c r="AJ83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>4cd28c40128e4079</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>0.556222</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>0.03699123076923083</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:39.880431Z</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="2" t="inlineStr"/>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr"/>
+      <c r="Z84" s="2" t="inlineStr"/>
+      <c r="AA84" s="2" t="inlineStr"/>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr"/>
+      <c r="AE84" s="2" t="inlineStr"/>
+      <c r="AF84" s="2" t="inlineStr"/>
+      <c r="AG84" s="2" t="inlineStr"/>
+      <c r="AH84" s="2" t="inlineStr"/>
+      <c r="AI84" s="2" t="inlineStr"/>
+      <c r="AJ84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2c489c1ad078402f</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>0.6138</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>0.0429845493562232</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:40.547769Z</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr"/>
+      <c r="Z85" s="2" t="inlineStr"/>
+      <c r="AA85" s="2" t="inlineStr"/>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr"/>
+      <c r="AE85" s="2" t="inlineStr"/>
+      <c r="AF85" s="2" t="inlineStr"/>
+      <c r="AG85" s="2" t="inlineStr"/>
+      <c r="AH85" s="2" t="inlineStr"/>
+      <c r="AI85" s="2" t="inlineStr"/>
+      <c r="AJ85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>d3a3f4d087654ccf</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>0.67501</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>0.07500999999999991</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:41.093797Z</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr"/>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Z86" s="2" t="inlineStr"/>
+      <c r="AA86" s="2" t="inlineStr"/>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr"/>
+      <c r="AE86" s="2" t="inlineStr"/>
+      <c r="AF86" s="2" t="inlineStr"/>
+      <c r="AG86" s="2" t="inlineStr"/>
+      <c r="AH86" s="2" t="inlineStr"/>
+      <c r="AI86" s="2" t="inlineStr"/>
+      <c r="AJ86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>40164056197b48ef</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>69617</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>0.626886</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>0.017511000000000054</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:50.955785Z</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr"/>
+      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr"/>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
+      <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr"/>
+      <c r="AG87" s="2" t="inlineStr"/>
+      <c r="AH87" s="2" t="inlineStr"/>
+      <c r="AI87" s="2" t="inlineStr"/>
+      <c r="AJ87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>3545cab16b434d08</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>0.551011</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>0.0608149215686275</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:24.737438Z</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="2" t="inlineStr"/>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr"/>
+      <c r="AE88" s="2" t="inlineStr"/>
+      <c r="AF88" s="2" t="inlineStr"/>
+      <c r="AG88" s="2" t="inlineStr"/>
+      <c r="AH88" s="2" t="inlineStr"/>
+      <c r="AI88" s="2" t="inlineStr"/>
+      <c r="AJ88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>94c526ff657540c1</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>71501</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>0.691594</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>0.11176206722689086</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:25.971824Z</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" s="2" t="inlineStr"/>
+      <c r="AA89" s="2" t="inlineStr"/>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+      <c r="AE89" s="2" t="inlineStr"/>
+      <c r="AF89" s="2" t="inlineStr"/>
+      <c r="AG89" s="2" t="inlineStr"/>
+      <c r="AH89" s="2" t="inlineStr"/>
+      <c r="AI89" s="2" t="inlineStr"/>
+      <c r="AJ89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>abf23fb0e1d341e2</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>0.698419</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>0.1886150784313726</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:41.500495Z</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr"/>
+      <c r="W90" s="2" t="inlineStr"/>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Z90" s="2" t="inlineStr"/>
+      <c r="AA90" s="2" t="inlineStr"/>
+      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr"/>
+      <c r="AE90" s="2" t="inlineStr"/>
+      <c r="AF90" s="2" t="inlineStr"/>
+      <c r="AG90" s="2" t="inlineStr"/>
+      <c r="AH90" s="2" t="inlineStr"/>
+      <c r="AI90" s="2" t="inlineStr"/>
+      <c r="AJ90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>8ac407b40d1543dd</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>0.556222</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>0.02570556807511737</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:42.051951Z</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="2" t="inlineStr"/>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr"/>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr"/>
+      <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
+      <c r="AG91" s="2" t="inlineStr"/>
+      <c r="AH91" s="2" t="inlineStr"/>
+      <c r="AI91" s="2" t="inlineStr"/>
+      <c r="AJ91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>34d37030a62041e4</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>0.6138</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>0.023636065573770515</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:42.609865Z</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr"/>
+      <c r="W92" s="2" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr"/>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+      <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
+      <c r="AG92" s="2" t="inlineStr"/>
+      <c r="AH92" s="2" t="inlineStr"/>
+      <c r="AI92" s="2" t="inlineStr"/>
+      <c r="AJ92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>e2067d694a6544b3</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>0.67501</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>0.0848460655737705</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:43.095313Z</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr"/>
+      <c r="W93" s="2" t="inlineStr"/>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr"/>
+      <c r="Z93" s="2" t="inlineStr"/>
+      <c r="AA93" s="2" t="inlineStr"/>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr"/>
+      <c r="AE93" s="2" t="inlineStr"/>
+      <c r="AF93" s="2" t="inlineStr"/>
+      <c r="AG93" s="2" t="inlineStr"/>
+      <c r="AH93" s="2" t="inlineStr"/>
+      <c r="AI93" s="2" t="inlineStr"/>
+      <c r="AJ93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>08e9c10923a24d98</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>69617</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>0.626886</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>0.017511000000000054</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:52.829078Z</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr"/>
+      <c r="Z94" s="2" t="inlineStr"/>
+      <c r="AA94" s="2" t="inlineStr"/>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr"/>
+      <c r="AE94" s="2" t="inlineStr"/>
+      <c r="AF94" s="2" t="inlineStr"/>
+      <c r="AG94" s="2" t="inlineStr"/>
+      <c r="AH94" s="2" t="inlineStr"/>
+      <c r="AI94" s="2" t="inlineStr"/>
+      <c r="AJ94" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ80"/>
+  <autoFilter ref="A1:AJ94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ94"/>
+  <dimension ref="A1:AJ116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -9534,14 +9534,34 @@
       <c r="W88" s="2" t="inlineStr"/>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y88" s="2" t="inlineStr"/>
-      <c r="Z88" s="2" t="inlineStr"/>
-      <c r="AA88" s="2" t="inlineStr"/>
-      <c r="AB88" s="2" t="inlineStr"/>
-      <c r="AC88" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>0.490000</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>-0.000196</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1.0400</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:59.329589Z</t>
+        </is>
+      </c>
       <c r="AD88" s="2" t="inlineStr"/>
       <c r="AE88" s="2" t="inlineStr"/>
       <c r="AF88" s="2" t="inlineStr"/>
@@ -9636,14 +9656,34 @@
       <c r="W89" s="2" t="inlineStr"/>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y89" s="2" t="inlineStr"/>
-      <c r="Z89" s="2" t="inlineStr"/>
-      <c r="AA89" s="2" t="inlineStr"/>
-      <c r="AB89" s="2" t="inlineStr"/>
-      <c r="AC89" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>0.580000</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>0.000168</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:00.632212Z</t>
+        </is>
+      </c>
       <c r="AD89" s="2" t="inlineStr"/>
       <c r="AE89" s="2" t="inlineStr"/>
       <c r="AF89" s="2" t="inlineStr"/>
@@ -10162,8 +10202,2252 @@
       <c r="AI94" s="2" t="inlineStr"/>
       <c r="AJ94" s="2" t="inlineStr"/>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>57e821831884465e</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>71337</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>0.571516</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>0.021966450450450536</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:51.128646Z</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="2" t="inlineStr"/>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr"/>
+      <c r="Z95" s="2" t="inlineStr"/>
+      <c r="AA95" s="2" t="inlineStr"/>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr"/>
+      <c r="AE95" s="2" t="inlineStr"/>
+      <c r="AF95" s="2" t="inlineStr"/>
+      <c r="AG95" s="2" t="inlineStr"/>
+      <c r="AH95" s="2" t="inlineStr"/>
+      <c r="AI95" s="2" t="inlineStr"/>
+      <c r="AJ95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>d3cd06fbe3cf4151</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>71339</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>0.681712</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>0.011745003300330015</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:52.174169Z</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:15:00Z</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr"/>
+      <c r="W96" s="2" t="inlineStr"/>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr"/>
+      <c r="Z96" s="2" t="inlineStr"/>
+      <c r="AA96" s="2" t="inlineStr"/>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr"/>
+      <c r="AE96" s="2" t="inlineStr"/>
+      <c r="AF96" s="2" t="inlineStr"/>
+      <c r="AG96" s="2" t="inlineStr"/>
+      <c r="AH96" s="2" t="inlineStr"/>
+      <c r="AI96" s="2" t="inlineStr"/>
+      <c r="AJ96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>41157a189b5943b1</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>0.674861</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>0.08469706557377055</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:56.359942Z</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr"/>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr"/>
+      <c r="Z97" s="2" t="inlineStr"/>
+      <c r="AA97" s="2" t="inlineStr"/>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr"/>
+      <c r="AE97" s="2" t="inlineStr"/>
+      <c r="AF97" s="2" t="inlineStr"/>
+      <c r="AG97" s="2" t="inlineStr"/>
+      <c r="AH97" s="2" t="inlineStr"/>
+      <c r="AI97" s="2" t="inlineStr"/>
+      <c r="AJ97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>e10fb1730f0d44aa</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>0.614064</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>0.023900065573770557</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:00.755213Z</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr"/>
+      <c r="W98" s="2" t="inlineStr"/>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr"/>
+      <c r="Z98" s="2" t="inlineStr"/>
+      <c r="AA98" s="2" t="inlineStr"/>
+      <c r="AB98" s="2" t="inlineStr"/>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr"/>
+      <c r="AE98" s="2" t="inlineStr"/>
+      <c r="AF98" s="2" t="inlineStr"/>
+      <c r="AG98" s="2" t="inlineStr"/>
+      <c r="AH98" s="2" t="inlineStr"/>
+      <c r="AI98" s="2" t="inlineStr"/>
+      <c r="AJ98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>7883d228b566428e</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>0.556108</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>0.036877230769230884</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:01.863539Z</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr"/>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr"/>
+      <c r="Z99" s="2" t="inlineStr"/>
+      <c r="AA99" s="2" t="inlineStr"/>
+      <c r="AB99" s="2" t="inlineStr"/>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr"/>
+      <c r="AE99" s="2" t="inlineStr"/>
+      <c r="AF99" s="2" t="inlineStr"/>
+      <c r="AG99" s="2" t="inlineStr"/>
+      <c r="AH99" s="2" t="inlineStr"/>
+      <c r="AI99" s="2" t="inlineStr"/>
+      <c r="AJ99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>233133a27b1a491f</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>0.698282</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>0.18847807843137254</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:03.034553Z</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr"/>
+      <c r="W100" s="2" t="inlineStr"/>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr"/>
+      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr"/>
+      <c r="AB100" s="2" t="inlineStr"/>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr"/>
+      <c r="AE100" s="2" t="inlineStr"/>
+      <c r="AF100" s="2" t="inlineStr"/>
+      <c r="AG100" s="2" t="inlineStr"/>
+      <c r="AH100" s="2" t="inlineStr"/>
+      <c r="AI100" s="2" t="inlineStr"/>
+      <c r="AJ100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>90defd682cc44db7</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>71391</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>0.645957</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>0.11544056807511738</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:05.325732Z</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr"/>
+      <c r="W101" s="2" t="inlineStr"/>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr"/>
+      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr"/>
+      <c r="AB101" s="2" t="inlineStr"/>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr"/>
+      <c r="AE101" s="2" t="inlineStr"/>
+      <c r="AF101" s="2" t="inlineStr"/>
+      <c r="AG101" s="2" t="inlineStr"/>
+      <c r="AH101" s="2" t="inlineStr"/>
+      <c r="AI101" s="2" t="inlineStr"/>
+      <c r="AJ101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>cb634daf9a874e20</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>71337</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>0.571449</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>0.021899450450450497</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:08.278263Z</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr"/>
+      <c r="W102" s="2" t="inlineStr"/>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr"/>
+      <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr"/>
+      <c r="AB102" s="2" t="inlineStr"/>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr"/>
+      <c r="AE102" s="2" t="inlineStr"/>
+      <c r="AF102" s="2" t="inlineStr"/>
+      <c r="AG102" s="2" t="inlineStr"/>
+      <c r="AH102" s="2" t="inlineStr"/>
+      <c r="AI102" s="2" t="inlineStr"/>
+      <c r="AJ102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>88c18daad2984df1</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>71339</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>0.681734</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>0.011767003300329981</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:10.074450Z</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:15:00Z</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr"/>
+      <c r="W103" s="2" t="inlineStr"/>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr"/>
+      <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr"/>
+      <c r="AB103" s="2" t="inlineStr"/>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr"/>
+      <c r="AE103" s="2" t="inlineStr"/>
+      <c r="AF103" s="2" t="inlineStr"/>
+      <c r="AG103" s="2" t="inlineStr"/>
+      <c r="AH103" s="2" t="inlineStr"/>
+      <c r="AI103" s="2" t="inlineStr"/>
+      <c r="AJ103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>c3a150cf96df48b6</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>0.67486</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>0.08469606557377052</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:11.142800Z</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr"/>
+      <c r="W104" s="2" t="inlineStr"/>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr"/>
+      <c r="Z104" s="2" t="inlineStr"/>
+      <c r="AA104" s="2" t="inlineStr"/>
+      <c r="AB104" s="2" t="inlineStr"/>
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="2" t="inlineStr"/>
+      <c r="AE104" s="2" t="inlineStr"/>
+      <c r="AF104" s="2" t="inlineStr"/>
+      <c r="AG104" s="2" t="inlineStr"/>
+      <c r="AH104" s="2" t="inlineStr"/>
+      <c r="AI104" s="2" t="inlineStr"/>
+      <c r="AJ104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>1a8c0de84de54a8a</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>71391</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>0.645876</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr"/>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>0.1850465069124424</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:12.914229Z</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr"/>
+      <c r="W105" s="2" t="inlineStr"/>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr"/>
+      <c r="Z105" s="2" t="inlineStr"/>
+      <c r="AA105" s="2" t="inlineStr"/>
+      <c r="AB105" s="2" t="inlineStr"/>
+      <c r="AC105" s="2" t="inlineStr"/>
+      <c r="AD105" s="2" t="inlineStr"/>
+      <c r="AE105" s="2" t="inlineStr"/>
+      <c r="AF105" s="2" t="inlineStr"/>
+      <c r="AG105" s="2" t="inlineStr"/>
+      <c r="AH105" s="2" t="inlineStr"/>
+      <c r="AI105" s="2" t="inlineStr"/>
+      <c r="AJ105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>a83a9ceb8b3144d1</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>0.556024</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>0.0367932307692308</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:14.595932Z</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr"/>
+      <c r="W106" s="2" t="inlineStr"/>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr"/>
+      <c r="Z106" s="2" t="inlineStr"/>
+      <c r="AA106" s="2" t="inlineStr"/>
+      <c r="AB106" s="2" t="inlineStr"/>
+      <c r="AC106" s="2" t="inlineStr"/>
+      <c r="AD106" s="2" t="inlineStr"/>
+      <c r="AE106" s="2" t="inlineStr"/>
+      <c r="AF106" s="2" t="inlineStr"/>
+      <c r="AG106" s="2" t="inlineStr"/>
+      <c r="AH106" s="2" t="inlineStr"/>
+      <c r="AI106" s="2" t="inlineStr"/>
+      <c r="AJ106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>a272e8ff382a4ce6</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>0.698177</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>0.18837307843137263</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:15.176846Z</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr"/>
+      <c r="W107" s="2" t="inlineStr"/>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr"/>
+      <c r="Z107" s="2" t="inlineStr"/>
+      <c r="AA107" s="2" t="inlineStr"/>
+      <c r="AB107" s="2" t="inlineStr"/>
+      <c r="AC107" s="2" t="inlineStr"/>
+      <c r="AD107" s="2" t="inlineStr"/>
+      <c r="AE107" s="2" t="inlineStr"/>
+      <c r="AF107" s="2" t="inlineStr"/>
+      <c r="AG107" s="2" t="inlineStr"/>
+      <c r="AH107" s="2" t="inlineStr"/>
+      <c r="AI107" s="2" t="inlineStr"/>
+      <c r="AJ107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>71a23ded7b754049</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>0.614141</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>0.034309067226890866</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:16.265161Z</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr"/>
+      <c r="W108" s="2" t="inlineStr"/>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr"/>
+      <c r="Z108" s="2" t="inlineStr"/>
+      <c r="AA108" s="2" t="inlineStr"/>
+      <c r="AB108" s="2" t="inlineStr"/>
+      <c r="AC108" s="2" t="inlineStr"/>
+      <c r="AD108" s="2" t="inlineStr"/>
+      <c r="AE108" s="2" t="inlineStr"/>
+      <c r="AF108" s="2" t="inlineStr"/>
+      <c r="AG108" s="2" t="inlineStr"/>
+      <c r="AH108" s="2" t="inlineStr"/>
+      <c r="AI108" s="2" t="inlineStr"/>
+      <c r="AJ108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>35f30b8453504198</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>71727</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>0.655018</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr"/>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>0.07518606722689081</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:18.645513Z</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr"/>
+      <c r="W109" s="2" t="inlineStr"/>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr"/>
+      <c r="Z109" s="2" t="inlineStr"/>
+      <c r="AA109" s="2" t="inlineStr"/>
+      <c r="AB109" s="2" t="inlineStr"/>
+      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AD109" s="2" t="inlineStr"/>
+      <c r="AE109" s="2" t="inlineStr"/>
+      <c r="AF109" s="2" t="inlineStr"/>
+      <c r="AG109" s="2" t="inlineStr"/>
+      <c r="AH109" s="2" t="inlineStr"/>
+      <c r="AI109" s="2" t="inlineStr"/>
+      <c r="AJ109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>f5598f266d3e4baa</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>71337</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>0.571449</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>0.021899450450450497</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:42.351782Z</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr"/>
+      <c r="W110" s="2" t="inlineStr"/>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr"/>
+      <c r="Z110" s="2" t="inlineStr"/>
+      <c r="AA110" s="2" t="inlineStr"/>
+      <c r="AB110" s="2" t="inlineStr"/>
+      <c r="AC110" s="2" t="inlineStr"/>
+      <c r="AD110" s="2" t="inlineStr"/>
+      <c r="AE110" s="2" t="inlineStr"/>
+      <c r="AF110" s="2" t="inlineStr"/>
+      <c r="AG110" s="2" t="inlineStr"/>
+      <c r="AH110" s="2" t="inlineStr"/>
+      <c r="AI110" s="2" t="inlineStr"/>
+      <c r="AJ110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>4e7394ef30204e89</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>71339</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>0.681734</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>0.011767003300329981</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:44.028305Z</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:15:00Z</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr"/>
+      <c r="W111" s="2" t="inlineStr"/>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr"/>
+      <c r="Z111" s="2" t="inlineStr"/>
+      <c r="AA111" s="2" t="inlineStr"/>
+      <c r="AB111" s="2" t="inlineStr"/>
+      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AD111" s="2" t="inlineStr"/>
+      <c r="AE111" s="2" t="inlineStr"/>
+      <c r="AF111" s="2" t="inlineStr"/>
+      <c r="AG111" s="2" t="inlineStr"/>
+      <c r="AH111" s="2" t="inlineStr"/>
+      <c r="AI111" s="2" t="inlineStr"/>
+      <c r="AJ111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>82331b00591c4401</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>0.67486</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>0.08469606557377052</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:45.147234Z</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr"/>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr"/>
+      <c r="Z112" s="2" t="inlineStr"/>
+      <c r="AA112" s="2" t="inlineStr"/>
+      <c r="AB112" s="2" t="inlineStr"/>
+      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AD112" s="2" t="inlineStr"/>
+      <c r="AE112" s="2" t="inlineStr"/>
+      <c r="AF112" s="2" t="inlineStr"/>
+      <c r="AG112" s="2" t="inlineStr"/>
+      <c r="AH112" s="2" t="inlineStr"/>
+      <c r="AI112" s="2" t="inlineStr"/>
+      <c r="AJ112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>c51b3e90707f4572</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>71391</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>0.645876</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr"/>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>0.145876</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:46.831301Z</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr"/>
+      <c r="W113" s="2" t="inlineStr"/>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr"/>
+      <c r="Z113" s="2" t="inlineStr"/>
+      <c r="AA113" s="2" t="inlineStr"/>
+      <c r="AB113" s="2" t="inlineStr"/>
+      <c r="AC113" s="2" t="inlineStr"/>
+      <c r="AD113" s="2" t="inlineStr"/>
+      <c r="AE113" s="2" t="inlineStr"/>
+      <c r="AF113" s="2" t="inlineStr"/>
+      <c r="AG113" s="2" t="inlineStr"/>
+      <c r="AH113" s="2" t="inlineStr"/>
+      <c r="AI113" s="2" t="inlineStr"/>
+      <c r="AJ113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>e391377abfea4fd2</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>0.556024</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>0.0367932307692308</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:48.498248Z</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr"/>
+      <c r="W114" s="2" t="inlineStr"/>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr"/>
+      <c r="AA114" s="2" t="inlineStr"/>
+      <c r="AB114" s="2" t="inlineStr"/>
+      <c r="AC114" s="2" t="inlineStr"/>
+      <c r="AD114" s="2" t="inlineStr"/>
+      <c r="AE114" s="2" t="inlineStr"/>
+      <c r="AF114" s="2" t="inlineStr"/>
+      <c r="AG114" s="2" t="inlineStr"/>
+      <c r="AH114" s="2" t="inlineStr"/>
+      <c r="AI114" s="2" t="inlineStr"/>
+      <c r="AJ114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>ed387ed6213c4d5d</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>0.698177</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>0.19817700000000005</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:49.093007Z</t>
+        </is>
+      </c>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr"/>
+      <c r="W115" s="2" t="inlineStr"/>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr"/>
+      <c r="AA115" s="2" t="inlineStr"/>
+      <c r="AB115" s="2" t="inlineStr"/>
+      <c r="AC115" s="2" t="inlineStr"/>
+      <c r="AD115" s="2" t="inlineStr"/>
+      <c r="AE115" s="2" t="inlineStr"/>
+      <c r="AF115" s="2" t="inlineStr"/>
+      <c r="AG115" s="2" t="inlineStr"/>
+      <c r="AH115" s="2" t="inlineStr"/>
+      <c r="AI115" s="2" t="inlineStr"/>
+      <c r="AJ115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>c97c74209f534ca2</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>0.614141</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>0.034309067226890866</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:50.211130Z</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr"/>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr"/>
+      <c r="AB116" s="2" t="inlineStr"/>
+      <c r="AC116" s="2" t="inlineStr"/>
+      <c r="AD116" s="2" t="inlineStr"/>
+      <c r="AE116" s="2" t="inlineStr"/>
+      <c r="AF116" s="2" t="inlineStr"/>
+      <c r="AG116" s="2" t="inlineStr"/>
+      <c r="AH116" s="2" t="inlineStr"/>
+      <c r="AI116" s="2" t="inlineStr"/>
+      <c r="AJ116" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ94"/>
+  <autoFilter ref="A1:AJ116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ116"/>
+  <dimension ref="A1:AJ152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7698,14 +7698,34 @@
       <c r="W70" s="2" t="inlineStr"/>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y70" s="2" t="inlineStr"/>
-      <c r="Z70" s="2" t="inlineStr"/>
-      <c r="AA70" s="2" t="inlineStr"/>
-      <c r="AB70" s="2" t="inlineStr"/>
-      <c r="AC70" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>0.600000</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:06:35.325761Z</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr"/>
       <c r="AE70" s="2" t="inlineStr"/>
       <c r="AF70" s="2" t="inlineStr"/>
@@ -12446,8 +12466,3780 @@
       <c r="AI116" s="2" t="inlineStr"/>
       <c r="AJ116" s="2" t="inlineStr"/>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>87e727f8e21f45b9</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>9cd22a347ddd07dcb14d465784988076b2f99aac119d8a8534a3e5b7ebfc248f</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>71337</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>0.571392</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>0.011920634361233473</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:04:19.465438Z</t>
+        </is>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr"/>
+      <c r="X117" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="AA117" s="2" t="inlineStr"/>
+      <c r="AB117" s="2" t="inlineStr"/>
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="2" t="inlineStr"/>
+      <c r="AE117" s="2" t="inlineStr"/>
+      <c r="AF117" s="2" t="inlineStr"/>
+      <c r="AG117" s="2" t="inlineStr"/>
+      <c r="AH117" s="2" t="inlineStr"/>
+      <c r="AI117" s="2" t="inlineStr"/>
+      <c r="AJ117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>e73de4b2e9954ad3</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>9cd22a347ddd07dcb14d465784988076b2f99aac119d8a8534a3e5b7ebfc248f</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>71339</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>0.681851</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>0.011884003300330015</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:04:22.864359Z</t>
+        </is>
+      </c>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:15:00Z</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr"/>
+      <c r="W118" s="2" t="inlineStr"/>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr"/>
+      <c r="Z118" s="2" t="inlineStr"/>
+      <c r="AA118" s="2" t="inlineStr"/>
+      <c r="AB118" s="2" t="inlineStr"/>
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="2" t="inlineStr"/>
+      <c r="AE118" s="2" t="inlineStr"/>
+      <c r="AF118" s="2" t="inlineStr"/>
+      <c r="AG118" s="2" t="inlineStr"/>
+      <c r="AH118" s="2" t="inlineStr"/>
+      <c r="AI118" s="2" t="inlineStr"/>
+      <c r="AJ118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>f68a9a500f7640ad</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>9cd22a347ddd07dcb14d465784988076b2f99aac119d8a8534a3e5b7ebfc248f</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>0.674837</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>0.08467306557377052</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:04:24.610010Z</t>
+        </is>
+      </c>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr"/>
+      <c r="W119" s="2" t="inlineStr"/>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="AA119" s="2" t="inlineStr"/>
+      <c r="AB119" s="2" t="inlineStr"/>
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="2" t="inlineStr"/>
+      <c r="AE119" s="2" t="inlineStr"/>
+      <c r="AF119" s="2" t="inlineStr"/>
+      <c r="AG119" s="2" t="inlineStr"/>
+      <c r="AH119" s="2" t="inlineStr"/>
+      <c r="AI119" s="2" t="inlineStr"/>
+      <c r="AJ119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>98d633a117be4428</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>9cd22a347ddd07dcb14d465784988076b2f99aac119d8a8534a3e5b7ebfc248f</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>0.555962</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>0.036731230769230794</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:04:26.981014Z</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr"/>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="AA120" s="2" t="inlineStr"/>
+      <c r="AB120" s="2" t="inlineStr"/>
+      <c r="AC120" s="2" t="inlineStr"/>
+      <c r="AD120" s="2" t="inlineStr"/>
+      <c r="AE120" s="2" t="inlineStr"/>
+      <c r="AF120" s="2" t="inlineStr"/>
+      <c r="AG120" s="2" t="inlineStr"/>
+      <c r="AH120" s="2" t="inlineStr"/>
+      <c r="AI120" s="2" t="inlineStr"/>
+      <c r="AJ120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>8193f7c6c4a5410e</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>9cd22a347ddd07dcb14d465784988076b2f99aac119d8a8534a3e5b7ebfc248f</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>71391</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>0.645844</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>0.09629445045045049</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:04:27.507136Z</t>
+        </is>
+      </c>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr"/>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr"/>
+      <c r="Z121" s="2" t="inlineStr"/>
+      <c r="AA121" s="2" t="inlineStr"/>
+      <c r="AB121" s="2" t="inlineStr"/>
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="2" t="inlineStr"/>
+      <c r="AE121" s="2" t="inlineStr"/>
+      <c r="AF121" s="2" t="inlineStr"/>
+      <c r="AG121" s="2" t="inlineStr"/>
+      <c r="AH121" s="2" t="inlineStr"/>
+      <c r="AI121" s="2" t="inlineStr"/>
+      <c r="AJ121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>c28e762678dd4fef</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>9cd22a347ddd07dcb14d465784988076b2f99aac119d8a8534a3e5b7ebfc248f</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>0.614248</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>0.034416067226890834</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:04:28.123105Z</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr"/>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr"/>
+      <c r="Z122" s="2" t="inlineStr"/>
+      <c r="AA122" s="2" t="inlineStr"/>
+      <c r="AB122" s="2" t="inlineStr"/>
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="2" t="inlineStr"/>
+      <c r="AE122" s="2" t="inlineStr"/>
+      <c r="AF122" s="2" t="inlineStr"/>
+      <c r="AG122" s="2" t="inlineStr"/>
+      <c r="AH122" s="2" t="inlineStr"/>
+      <c r="AI122" s="2" t="inlineStr"/>
+      <c r="AJ122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>1b37a15f2e17455f</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>9cd22a347ddd07dcb14d465784988076b2f99aac119d8a8534a3e5b7ebfc248f</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>0.698162</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>0.19816199999999995</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:04:29.881850Z</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr"/>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr"/>
+      <c r="Z123" s="2" t="inlineStr"/>
+      <c r="AA123" s="2" t="inlineStr"/>
+      <c r="AB123" s="2" t="inlineStr"/>
+      <c r="AC123" s="2" t="inlineStr"/>
+      <c r="AD123" s="2" t="inlineStr"/>
+      <c r="AE123" s="2" t="inlineStr"/>
+      <c r="AF123" s="2" t="inlineStr"/>
+      <c r="AG123" s="2" t="inlineStr"/>
+      <c r="AH123" s="2" t="inlineStr"/>
+      <c r="AI123" s="2" t="inlineStr"/>
+      <c r="AJ123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>6caf0706ecf1437d</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>9cd22a347ddd07dcb14d465784988076b2f99aac119d8a8534a3e5b7ebfc248f</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>71727</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>0.654989</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>0.014701230215827366</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:04:32.846756Z</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr"/>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr"/>
+      <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr"/>
+      <c r="AB124" s="2" t="inlineStr"/>
+      <c r="AC124" s="2" t="inlineStr"/>
+      <c r="AD124" s="2" t="inlineStr"/>
+      <c r="AE124" s="2" t="inlineStr"/>
+      <c r="AF124" s="2" t="inlineStr"/>
+      <c r="AG124" s="2" t="inlineStr"/>
+      <c r="AH124" s="2" t="inlineStr"/>
+      <c r="AI124" s="2" t="inlineStr"/>
+      <c r="AJ124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>bec5a25aca444647</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>87e73f3e8c33751dbc7005b4404d0ee0ac9b9f8c3869a8f2e7fbc367004c2f64</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>71337</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>0.580391</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr"/>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>0.020919634361233452</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:54:14.340644Z</t>
+        </is>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr"/>
+      <c r="W125" s="2" t="inlineStr"/>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z125" s="2" t="inlineStr">
+        <is>
+          <t>0.560000</t>
+        </is>
+      </c>
+      <c r="AA125" s="2" t="inlineStr">
+        <is>
+          <t>0.000529</t>
+        </is>
+      </c>
+      <c r="AB125" s="2" t="inlineStr">
+        <is>
+          <t>0.9843</t>
+        </is>
+      </c>
+      <c r="AC125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:49.453936Z</t>
+        </is>
+      </c>
+      <c r="AD125" s="2" t="inlineStr"/>
+      <c r="AE125" s="2" t="inlineStr"/>
+      <c r="AF125" s="2" t="inlineStr"/>
+      <c r="AG125" s="2" t="inlineStr"/>
+      <c r="AH125" s="2" t="inlineStr"/>
+      <c r="AI125" s="2" t="inlineStr"/>
+      <c r="AJ125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>069ea2f623b64b71</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>87e73f3e8c33751dbc7005b4404d0ee0ac9b9f8c3869a8f2e7fbc367004c2f64</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>71391</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>0.609175</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>0.049703634361233484</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:54:19.234049Z</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr"/>
+      <c r="W126" s="2" t="inlineStr"/>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr"/>
+      <c r="Z126" s="2" t="inlineStr"/>
+      <c r="AA126" s="2" t="inlineStr"/>
+      <c r="AB126" s="2" t="inlineStr"/>
+      <c r="AC126" s="2" t="inlineStr"/>
+      <c r="AD126" s="2" t="inlineStr"/>
+      <c r="AE126" s="2" t="inlineStr"/>
+      <c r="AF126" s="2" t="inlineStr"/>
+      <c r="AG126" s="2" t="inlineStr"/>
+      <c r="AH126" s="2" t="inlineStr"/>
+      <c r="AI126" s="2" t="inlineStr"/>
+      <c r="AJ126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>cf98a208e65747b9</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>87e73f3e8c33751dbc7005b4404d0ee0ac9b9f8c3869a8f2e7fbc367004c2f64</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>0.684525</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr"/>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>0.17472107843137263</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:54:20.601948Z</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr"/>
+      <c r="W127" s="2" t="inlineStr"/>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr"/>
+      <c r="Z127" s="2" t="inlineStr"/>
+      <c r="AA127" s="2" t="inlineStr"/>
+      <c r="AB127" s="2" t="inlineStr"/>
+      <c r="AC127" s="2" t="inlineStr"/>
+      <c r="AD127" s="2" t="inlineStr"/>
+      <c r="AE127" s="2" t="inlineStr"/>
+      <c r="AF127" s="2" t="inlineStr"/>
+      <c r="AG127" s="2" t="inlineStr"/>
+      <c r="AH127" s="2" t="inlineStr"/>
+      <c r="AI127" s="2" t="inlineStr"/>
+      <c r="AJ127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>c1f38895299c4122</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>87e73f3e8c33751dbc7005b4404d0ee0ac9b9f8c3869a8f2e7fbc367004c2f64</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>0.556406</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>0.02588956807511733</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:54:21.330964Z</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr"/>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr"/>
+      <c r="AB128" s="2" t="inlineStr"/>
+      <c r="AC128" s="2" t="inlineStr"/>
+      <c r="AD128" s="2" t="inlineStr"/>
+      <c r="AE128" s="2" t="inlineStr"/>
+      <c r="AF128" s="2" t="inlineStr"/>
+      <c r="AG128" s="2" t="inlineStr"/>
+      <c r="AH128" s="2" t="inlineStr"/>
+      <c r="AI128" s="2" t="inlineStr"/>
+      <c r="AJ128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>3d1f1e6c4a114c99</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>87e73f3e8c33751dbc7005b4404d0ee0ac9b9f8c3869a8f2e7fbc367004c2f64</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>0.595487</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr"/>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>0.015655067226890806</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:54:21.893093Z</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr"/>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr"/>
+      <c r="AB129" s="2" t="inlineStr"/>
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="2" t="inlineStr"/>
+      <c r="AE129" s="2" t="inlineStr"/>
+      <c r="AF129" s="2" t="inlineStr"/>
+      <c r="AG129" s="2" t="inlineStr"/>
+      <c r="AH129" s="2" t="inlineStr"/>
+      <c r="AI129" s="2" t="inlineStr"/>
+      <c r="AJ129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2af46f7593ff41b3</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>87e73f3e8c33751dbc7005b4404d0ee0ac9b9f8c3869a8f2e7fbc367004c2f64</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>0.675209</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>0.19443976923076922</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:54:25.072684Z</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr"/>
+      <c r="W130" s="2" t="inlineStr"/>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr"/>
+      <c r="Z130" s="2" t="inlineStr"/>
+      <c r="AA130" s="2" t="inlineStr"/>
+      <c r="AB130" s="2" t="inlineStr"/>
+      <c r="AC130" s="2" t="inlineStr"/>
+      <c r="AD130" s="2" t="inlineStr"/>
+      <c r="AE130" s="2" t="inlineStr"/>
+      <c r="AF130" s="2" t="inlineStr"/>
+      <c r="AG130" s="2" t="inlineStr"/>
+      <c r="AH130" s="2" t="inlineStr"/>
+      <c r="AI130" s="2" t="inlineStr"/>
+      <c r="AJ130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>def9fbaf98794772</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>87e73f3e8c33751dbc7005b4404d0ee0ac9b9f8c3869a8f2e7fbc367004c2f64</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>71795</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>0.53492</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr"/>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr"/>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>0.13491999999999993</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:54:32.019236Z</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr"/>
+      <c r="W131" s="2" t="inlineStr"/>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr"/>
+      <c r="AB131" s="2" t="inlineStr"/>
+      <c r="AC131" s="2" t="inlineStr"/>
+      <c r="AD131" s="2" t="inlineStr"/>
+      <c r="AE131" s="2" t="inlineStr"/>
+      <c r="AF131" s="2" t="inlineStr"/>
+      <c r="AG131" s="2" t="inlineStr"/>
+      <c r="AH131" s="2" t="inlineStr"/>
+      <c r="AI131" s="2" t="inlineStr"/>
+      <c r="AJ131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>5d2786f97a50491b</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>71391</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>0.633669</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr"/>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>0.0741976343612335</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:08:12.712388Z</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr"/>
+      <c r="W132" s="2" t="inlineStr"/>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z132" s="2" t="inlineStr">
+        <is>
+          <t>0.560000</t>
+        </is>
+      </c>
+      <c r="AA132" s="2" t="inlineStr">
+        <is>
+          <t>0.000529</t>
+        </is>
+      </c>
+      <c r="AB132" s="2" t="inlineStr">
+        <is>
+          <t>-1.5000</t>
+        </is>
+      </c>
+      <c r="AC132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:01.245023Z</t>
+        </is>
+      </c>
+      <c r="AD132" s="2" t="inlineStr"/>
+      <c r="AE132" s="2" t="inlineStr"/>
+      <c r="AF132" s="2" t="inlineStr"/>
+      <c r="AG132" s="2" t="inlineStr"/>
+      <c r="AH132" s="2" t="inlineStr"/>
+      <c r="AI132" s="2" t="inlineStr"/>
+      <c r="AJ132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>29168cf5f2d74966</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>0.684275</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr"/>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr"/>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>0.17447107843137255</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:08:14.227023Z</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr"/>
+      <c r="W133" s="2" t="inlineStr"/>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z133" s="2" t="inlineStr">
+        <is>
+          <t>0.510000</t>
+        </is>
+      </c>
+      <c r="AA133" s="2" t="inlineStr">
+        <is>
+          <t>0.000196</t>
+        </is>
+      </c>
+      <c r="AB133" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:06:37.278470Z</t>
+        </is>
+      </c>
+      <c r="AD133" s="2" t="inlineStr"/>
+      <c r="AE133" s="2" t="inlineStr"/>
+      <c r="AF133" s="2" t="inlineStr"/>
+      <c r="AG133" s="2" t="inlineStr"/>
+      <c r="AH133" s="2" t="inlineStr"/>
+      <c r="AI133" s="2" t="inlineStr"/>
+      <c r="AJ133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>df7a0759732b4011</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>0.556272</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>0.025755568075117363</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:08:15.431614Z</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr"/>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z134" s="2" t="inlineStr">
+        <is>
+          <t>0.530000</t>
+        </is>
+      </c>
+      <c r="AA134" s="2" t="inlineStr">
+        <is>
+          <t>-0.000516</t>
+        </is>
+      </c>
+      <c r="AB134" s="2" t="inlineStr">
+        <is>
+          <t>0.8850</t>
+        </is>
+      </c>
+      <c r="AC134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:03.567608Z</t>
+        </is>
+      </c>
+      <c r="AD134" s="2" t="inlineStr"/>
+      <c r="AE134" s="2" t="inlineStr"/>
+      <c r="AF134" s="2" t="inlineStr"/>
+      <c r="AG134" s="2" t="inlineStr"/>
+      <c r="AH134" s="2" t="inlineStr"/>
+      <c r="AI134" s="2" t="inlineStr"/>
+      <c r="AJ134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>12a36fb18bb841e0</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>0.595428</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr"/>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>0.015596067226890775</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:08:16.175127Z</t>
+        </is>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr"/>
+      <c r="W135" s="2" t="inlineStr"/>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr"/>
+      <c r="AB135" s="2" t="inlineStr"/>
+      <c r="AC135" s="2" t="inlineStr"/>
+      <c r="AD135" s="2" t="inlineStr"/>
+      <c r="AE135" s="2" t="inlineStr"/>
+      <c r="AF135" s="2" t="inlineStr"/>
+      <c r="AG135" s="2" t="inlineStr"/>
+      <c r="AH135" s="2" t="inlineStr"/>
+      <c r="AI135" s="2" t="inlineStr"/>
+      <c r="AJ135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>25d6c1d93ca547c5</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>0.674864</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr"/>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>0.2140345069124424</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:08:19.220614Z</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr"/>
+      <c r="W136" s="2" t="inlineStr"/>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y136" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z136" s="2" t="inlineStr">
+        <is>
+          <t>0.460000</t>
+        </is>
+      </c>
+      <c r="AA136" s="2" t="inlineStr">
+        <is>
+          <t>-0.000829</t>
+        </is>
+      </c>
+      <c r="AB136" s="2" t="inlineStr">
+        <is>
+          <t>-1.7500</t>
+        </is>
+      </c>
+      <c r="AC136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:05.849023Z</t>
+        </is>
+      </c>
+      <c r="AD136" s="2" t="inlineStr"/>
+      <c r="AE136" s="2" t="inlineStr"/>
+      <c r="AF136" s="2" t="inlineStr"/>
+      <c r="AG136" s="2" t="inlineStr"/>
+      <c r="AH136" s="2" t="inlineStr"/>
+      <c r="AI136" s="2" t="inlineStr"/>
+      <c r="AJ136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>4e52261f6d184f9b</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>71795</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>0.534806</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr"/>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr"/>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>0.13480599999999998</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:08:25.394342Z</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr"/>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr"/>
+      <c r="Z137" s="2" t="inlineStr"/>
+      <c r="AA137" s="2" t="inlineStr"/>
+      <c r="AB137" s="2" t="inlineStr"/>
+      <c r="AC137" s="2" t="inlineStr"/>
+      <c r="AD137" s="2" t="inlineStr"/>
+      <c r="AE137" s="2" t="inlineStr"/>
+      <c r="AF137" s="2" t="inlineStr"/>
+      <c r="AG137" s="2" t="inlineStr"/>
+      <c r="AH137" s="2" t="inlineStr"/>
+      <c r="AI137" s="2" t="inlineStr"/>
+      <c r="AJ137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>9d94dd36eb1247aa</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>8795a61e8f63d68dc2d05b6316d1dba950c17433ebbc32b270602b097234465f</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>71795</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>0.53495</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>0.14432500000000004</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:02:43.787740Z</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr"/>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y138" s="2" t="inlineStr"/>
+      <c r="Z138" s="2" t="inlineStr"/>
+      <c r="AA138" s="2" t="inlineStr"/>
+      <c r="AB138" s="2" t="inlineStr"/>
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="2" t="inlineStr"/>
+      <c r="AE138" s="2" t="inlineStr"/>
+      <c r="AF138" s="2" t="inlineStr"/>
+      <c r="AG138" s="2" t="inlineStr"/>
+      <c r="AH138" s="2" t="inlineStr"/>
+      <c r="AI138" s="2" t="inlineStr"/>
+      <c r="AJ138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>605cbeb1f3f34a9f</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>d19dfbfe37522ea9eea09d96cb6f2d260c1d592ddf72d14516ce18489a271742</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>71795</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>0.534906</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr"/>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr"/>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>0.144281</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:10:43.268337Z</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr"/>
+      <c r="W139" s="2" t="inlineStr"/>
+      <c r="X139" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y139" s="2" t="inlineStr"/>
+      <c r="Z139" s="2" t="inlineStr"/>
+      <c r="AA139" s="2" t="inlineStr"/>
+      <c r="AB139" s="2" t="inlineStr"/>
+      <c r="AC139" s="2" t="inlineStr"/>
+      <c r="AD139" s="2" t="inlineStr"/>
+      <c r="AE139" s="2" t="inlineStr"/>
+      <c r="AF139" s="2" t="inlineStr"/>
+      <c r="AG139" s="2" t="inlineStr"/>
+      <c r="AH139" s="2" t="inlineStr"/>
+      <c r="AI139" s="2" t="inlineStr"/>
+      <c r="AJ139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>550b293478f749ab</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>d19dfbfe37522ea9eea09d96cb6f2d260c1d592ddf72d14516ce18489a271742</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>72536</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>0.553497</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr"/>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>0.034266230769230854</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:11:05.461127Z</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr"/>
+      <c r="W140" s="2" t="inlineStr"/>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y140" s="2" t="inlineStr"/>
+      <c r="Z140" s="2" t="inlineStr"/>
+      <c r="AA140" s="2" t="inlineStr"/>
+      <c r="AB140" s="2" t="inlineStr"/>
+      <c r="AC140" s="2" t="inlineStr"/>
+      <c r="AD140" s="2" t="inlineStr"/>
+      <c r="AE140" s="2" t="inlineStr"/>
+      <c r="AF140" s="2" t="inlineStr"/>
+      <c r="AG140" s="2" t="inlineStr"/>
+      <c r="AH140" s="2" t="inlineStr"/>
+      <c r="AI140" s="2" t="inlineStr"/>
+      <c r="AJ140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2b318a697f2545c9</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>d99ca9864e2948831e50bdac381f2142fecb1c258ef612db03b007e8bc539ea0</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>71795</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>0.5349</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr"/>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr"/>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>0.14427500000000004</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:25.720961Z</t>
+        </is>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr"/>
+      <c r="W141" s="2" t="inlineStr"/>
+      <c r="X141" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y141" s="2" t="inlineStr"/>
+      <c r="Z141" s="2" t="inlineStr"/>
+      <c r="AA141" s="2" t="inlineStr"/>
+      <c r="AB141" s="2" t="inlineStr"/>
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="2" t="inlineStr"/>
+      <c r="AE141" s="2" t="inlineStr"/>
+      <c r="AF141" s="2" t="inlineStr"/>
+      <c r="AG141" s="2" t="inlineStr"/>
+      <c r="AH141" s="2" t="inlineStr"/>
+      <c r="AI141" s="2" t="inlineStr"/>
+      <c r="AJ141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>fb11a4f6ac2f460b</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>d99ca9864e2948831e50bdac381f2142fecb1c258ef612db03b007e8bc539ea0</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>72488</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>0.697356</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr"/>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>0.027389003300330006</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:38.482064Z</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr"/>
+      <c r="W142" s="2" t="inlineStr"/>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr"/>
+      <c r="Z142" s="2" t="inlineStr"/>
+      <c r="AA142" s="2" t="inlineStr"/>
+      <c r="AB142" s="2" t="inlineStr"/>
+      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AD142" s="2" t="inlineStr"/>
+      <c r="AE142" s="2" t="inlineStr"/>
+      <c r="AF142" s="2" t="inlineStr"/>
+      <c r="AG142" s="2" t="inlineStr"/>
+      <c r="AH142" s="2" t="inlineStr"/>
+      <c r="AI142" s="2" t="inlineStr"/>
+      <c r="AJ142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>3bec34ee29804f23</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>d99ca9864e2948831e50bdac381f2142fecb1c258ef612db03b007e8bc539ea0</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>72533</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>0.634466</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr"/>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr"/>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>0.18401554954954946</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:40.665340Z</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr"/>
+      <c r="W143" s="2" t="inlineStr"/>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="AA143" s="2" t="inlineStr"/>
+      <c r="AB143" s="2" t="inlineStr"/>
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="2" t="inlineStr"/>
+      <c r="AE143" s="2" t="inlineStr"/>
+      <c r="AF143" s="2" t="inlineStr"/>
+      <c r="AG143" s="2" t="inlineStr"/>
+      <c r="AH143" s="2" t="inlineStr"/>
+      <c r="AI143" s="2" t="inlineStr"/>
+      <c r="AJ143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>a218918c801c4b99</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>d99ca9864e2948831e50bdac381f2142fecb1c258ef612db03b007e8bc539ea0</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>70562</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>0.60674</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr"/>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr"/>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>0.14591050691244234</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:55.046930Z</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr"/>
+      <c r="W144" s="2" t="inlineStr"/>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="AA144" s="2" t="inlineStr"/>
+      <c r="AB144" s="2" t="inlineStr"/>
+      <c r="AC144" s="2" t="inlineStr"/>
+      <c r="AD144" s="2" t="inlineStr"/>
+      <c r="AE144" s="2" t="inlineStr"/>
+      <c r="AF144" s="2" t="inlineStr"/>
+      <c r="AG144" s="2" t="inlineStr"/>
+      <c r="AH144" s="2" t="inlineStr"/>
+      <c r="AI144" s="2" t="inlineStr"/>
+      <c r="AJ144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>7a070d79543743a8</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>d99ca9864e2948831e50bdac381f2142fecb1c258ef612db03b007e8bc539ea0</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>70787</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>0.608329</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr"/>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr"/>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>0.0375135493562232</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:59.095017Z</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr"/>
+      <c r="W145" s="2" t="inlineStr"/>
+      <c r="X145" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y145" s="2" t="inlineStr"/>
+      <c r="Z145" s="2" t="inlineStr"/>
+      <c r="AA145" s="2" t="inlineStr"/>
+      <c r="AB145" s="2" t="inlineStr"/>
+      <c r="AC145" s="2" t="inlineStr"/>
+      <c r="AD145" s="2" t="inlineStr"/>
+      <c r="AE145" s="2" t="inlineStr"/>
+      <c r="AF145" s="2" t="inlineStr"/>
+      <c r="AG145" s="2" t="inlineStr"/>
+      <c r="AH145" s="2" t="inlineStr"/>
+      <c r="AI145" s="2" t="inlineStr"/>
+      <c r="AJ145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>ece6f3afad914938</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>d99ca9864e2948831e50bdac381f2142fecb1c258ef612db03b007e8bc539ea0</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>70599</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>0.572228</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr"/>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>0.02267845045045047</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:27:59.907351Z</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr"/>
+      <c r="W146" s="2" t="inlineStr"/>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y146" s="2" t="inlineStr"/>
+      <c r="Z146" s="2" t="inlineStr"/>
+      <c r="AA146" s="2" t="inlineStr"/>
+      <c r="AB146" s="2" t="inlineStr"/>
+      <c r="AC146" s="2" t="inlineStr"/>
+      <c r="AD146" s="2" t="inlineStr"/>
+      <c r="AE146" s="2" t="inlineStr"/>
+      <c r="AF146" s="2" t="inlineStr"/>
+      <c r="AG146" s="2" t="inlineStr"/>
+      <c r="AH146" s="2" t="inlineStr"/>
+      <c r="AI146" s="2" t="inlineStr"/>
+      <c r="AJ146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>31aa512d15894af3</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>d99ca9864e2948831e50bdac381f2142fecb1c258ef612db03b007e8bc539ea0</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>72653</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>0.712843</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr"/>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr"/>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>0.013143300300300309</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:28:12.450584Z</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr"/>
+      <c r="W147" s="2" t="inlineStr"/>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr"/>
+      <c r="AB147" s="2" t="inlineStr"/>
+      <c r="AC147" s="2" t="inlineStr"/>
+      <c r="AD147" s="2" t="inlineStr"/>
+      <c r="AE147" s="2" t="inlineStr"/>
+      <c r="AF147" s="2" t="inlineStr"/>
+      <c r="AG147" s="2" t="inlineStr"/>
+      <c r="AH147" s="2" t="inlineStr"/>
+      <c r="AI147" s="2" t="inlineStr"/>
+      <c r="AJ147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>20b45384918340f5</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>71795</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>0.5349</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr"/>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>0.14427500000000004</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:15.635268Z</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr"/>
+      <c r="W148" s="2" t="inlineStr"/>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr"/>
+      <c r="AB148" s="2" t="inlineStr"/>
+      <c r="AC148" s="2" t="inlineStr"/>
+      <c r="AD148" s="2" t="inlineStr"/>
+      <c r="AE148" s="2" t="inlineStr"/>
+      <c r="AF148" s="2" t="inlineStr"/>
+      <c r="AG148" s="2" t="inlineStr"/>
+      <c r="AH148" s="2" t="inlineStr"/>
+      <c r="AI148" s="2" t="inlineStr"/>
+      <c r="AJ148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>78f0efc0b84d4f17</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>72488</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>0.697347</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr"/>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr"/>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>0.02738000330033008</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:28.087442Z</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr"/>
+      <c r="W149" s="2" t="inlineStr"/>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr"/>
+      <c r="AB149" s="2" t="inlineStr"/>
+      <c r="AC149" s="2" t="inlineStr"/>
+      <c r="AD149" s="2" t="inlineStr"/>
+      <c r="AE149" s="2" t="inlineStr"/>
+      <c r="AF149" s="2" t="inlineStr"/>
+      <c r="AG149" s="2" t="inlineStr"/>
+      <c r="AH149" s="2" t="inlineStr"/>
+      <c r="AI149" s="2" t="inlineStr"/>
+      <c r="AJ149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>766c2687135148a8</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>72533</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>0.63446</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr"/>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr"/>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>0.1840095495495495</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:29.742606Z</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr"/>
+      <c r="W150" s="2" t="inlineStr"/>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr"/>
+      <c r="AB150" s="2" t="inlineStr"/>
+      <c r="AC150" s="2" t="inlineStr"/>
+      <c r="AD150" s="2" t="inlineStr"/>
+      <c r="AE150" s="2" t="inlineStr"/>
+      <c r="AF150" s="2" t="inlineStr"/>
+      <c r="AG150" s="2" t="inlineStr"/>
+      <c r="AH150" s="2" t="inlineStr"/>
+      <c r="AI150" s="2" t="inlineStr"/>
+      <c r="AJ150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>7a87f1b466574957</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>70562</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>0.606734</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr"/>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr"/>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>0.16620536563876653</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:44.309251Z</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr"/>
+      <c r="W151" s="2" t="inlineStr"/>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr"/>
+      <c r="AB151" s="2" t="inlineStr"/>
+      <c r="AC151" s="2" t="inlineStr"/>
+      <c r="AD151" s="2" t="inlineStr"/>
+      <c r="AE151" s="2" t="inlineStr"/>
+      <c r="AF151" s="2" t="inlineStr"/>
+      <c r="AG151" s="2" t="inlineStr"/>
+      <c r="AH151" s="2" t="inlineStr"/>
+      <c r="AI151" s="2" t="inlineStr"/>
+      <c r="AJ151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>5c2efc43d2e840e1</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>70787</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>0.608323</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr"/>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr"/>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>0.037507549356223135</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:48.579124Z</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr"/>
+      <c r="W152" s="2" t="inlineStr"/>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr"/>
+      <c r="AB152" s="2" t="inlineStr"/>
+      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AD152" s="2" t="inlineStr"/>
+      <c r="AE152" s="2" t="inlineStr"/>
+      <c r="AF152" s="2" t="inlineStr"/>
+      <c r="AG152" s="2" t="inlineStr"/>
+      <c r="AH152" s="2" t="inlineStr"/>
+      <c r="AI152" s="2" t="inlineStr"/>
+      <c r="AJ152" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ116"/>
+  <autoFilter ref="A1:AJ152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ152"/>
+  <dimension ref="A1:AJ172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -15814,14 +15814,34 @@
       <c r="W148" s="2" t="inlineStr"/>
       <c r="X148" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y148" s="2" t="inlineStr"/>
-      <c r="Z148" s="2" t="inlineStr"/>
-      <c r="AA148" s="2" t="inlineStr"/>
-      <c r="AB148" s="2" t="inlineStr"/>
-      <c r="AC148" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z148" s="2" t="inlineStr">
+        <is>
+          <t>0.390000</t>
+        </is>
+      </c>
+      <c r="AA148" s="2" t="inlineStr">
+        <is>
+          <t>-0.000625</t>
+        </is>
+      </c>
+      <c r="AB148" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:51:52.887177Z</t>
+        </is>
+      </c>
       <c r="AD148" s="2" t="inlineStr"/>
       <c r="AE148" s="2" t="inlineStr"/>
       <c r="AF148" s="2" t="inlineStr"/>
@@ -16238,8 +16258,2048 @@
       <c r="AI152" s="2" t="inlineStr"/>
       <c r="AJ152" s="2" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>82c19c2dd0624fa4</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>eeb9a1d5ce74a7256c828bdbb2e18493fbe1e9cfd6bbc8bfbc2b94856dda2a21</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>72488</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>0.69703</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr"/>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr"/>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>0.02706300330033007</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:23.330693Z</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr"/>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr"/>
+      <c r="AB153" s="2" t="inlineStr"/>
+      <c r="AC153" s="2" t="inlineStr"/>
+      <c r="AD153" s="2" t="inlineStr"/>
+      <c r="AE153" s="2" t="inlineStr"/>
+      <c r="AF153" s="2" t="inlineStr"/>
+      <c r="AG153" s="2" t="inlineStr"/>
+      <c r="AH153" s="2" t="inlineStr"/>
+      <c r="AI153" s="2" t="inlineStr"/>
+      <c r="AJ153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>3864d3e33bd342ea</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>eeb9a1d5ce74a7256c828bdbb2e18493fbe1e9cfd6bbc8bfbc2b94856dda2a21</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>72533</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>0.634335</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr"/>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr"/>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>0.21416693277310922</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:25.333811Z</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr"/>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr"/>
+      <c r="AB154" s="2" t="inlineStr"/>
+      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AD154" s="2" t="inlineStr"/>
+      <c r="AE154" s="2" t="inlineStr"/>
+      <c r="AF154" s="2" t="inlineStr"/>
+      <c r="AG154" s="2" t="inlineStr"/>
+      <c r="AH154" s="2" t="inlineStr"/>
+      <c r="AI154" s="2" t="inlineStr"/>
+      <c r="AJ154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>961004f9738a4e88</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>eeb9a1d5ce74a7256c828bdbb2e18493fbe1e9cfd6bbc8bfbc2b94856dda2a21</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>72490</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>0.531297</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr"/>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr"/>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>0.11112893277310926</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:35.809740Z</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr"/>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr"/>
+      <c r="AB155" s="2" t="inlineStr"/>
+      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AD155" s="2" t="inlineStr"/>
+      <c r="AE155" s="2" t="inlineStr"/>
+      <c r="AF155" s="2" t="inlineStr"/>
+      <c r="AG155" s="2" t="inlineStr"/>
+      <c r="AH155" s="2" t="inlineStr"/>
+      <c r="AI155" s="2" t="inlineStr"/>
+      <c r="AJ155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>56dc253617af40db</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>eeb9a1d5ce74a7256c828bdbb2e18493fbe1e9cfd6bbc8bfbc2b94856dda2a21</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>70562</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>0.606569</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr"/>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr"/>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>0.14573950691244242</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:37.118883Z</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
+      <c r="W156" s="2" t="inlineStr"/>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr"/>
+      <c r="AB156" s="2" t="inlineStr"/>
+      <c r="AC156" s="2" t="inlineStr"/>
+      <c r="AD156" s="2" t="inlineStr"/>
+      <c r="AE156" s="2" t="inlineStr"/>
+      <c r="AF156" s="2" t="inlineStr"/>
+      <c r="AG156" s="2" t="inlineStr"/>
+      <c r="AH156" s="2" t="inlineStr"/>
+      <c r="AI156" s="2" t="inlineStr"/>
+      <c r="AJ156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>e769c1f13b4b42a8</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>eeb9a1d5ce74a7256c828bdbb2e18493fbe1e9cfd6bbc8bfbc2b94856dda2a21</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>70787</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>0.608253</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr"/>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr"/>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>0.048781634361233506</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:38.335115Z</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr"/>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr"/>
+      <c r="AB157" s="2" t="inlineStr"/>
+      <c r="AC157" s="2" t="inlineStr"/>
+      <c r="AD157" s="2" t="inlineStr"/>
+      <c r="AE157" s="2" t="inlineStr"/>
+      <c r="AF157" s="2" t="inlineStr"/>
+      <c r="AG157" s="2" t="inlineStr"/>
+      <c r="AH157" s="2" t="inlineStr"/>
+      <c r="AI157" s="2" t="inlineStr"/>
+      <c r="AJ157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>0dbd17f49ef74979</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>eeb9a1d5ce74a7256c828bdbb2e18493fbe1e9cfd6bbc8bfbc2b94856dda2a21</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>72651</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>0.747088</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr"/>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>0.1975384504504505</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:45.609544Z</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr"/>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr"/>
+      <c r="AB158" s="2" t="inlineStr"/>
+      <c r="AC158" s="2" t="inlineStr"/>
+      <c r="AD158" s="2" t="inlineStr"/>
+      <c r="AE158" s="2" t="inlineStr"/>
+      <c r="AF158" s="2" t="inlineStr"/>
+      <c r="AG158" s="2" t="inlineStr"/>
+      <c r="AH158" s="2" t="inlineStr"/>
+      <c r="AI158" s="2" t="inlineStr"/>
+      <c r="AJ158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>afbcbd29cbb541c8</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>5ed7c189c90211b472ec0214d2b7901a8b9cb103b2be3f5519c68e215b46057f</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>72533</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>0.634324</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr"/>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr"/>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>0.243699</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:38.425700Z</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr"/>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr"/>
+      <c r="AB159" s="2" t="inlineStr"/>
+      <c r="AC159" s="2" t="inlineStr"/>
+      <c r="AD159" s="2" t="inlineStr"/>
+      <c r="AE159" s="2" t="inlineStr"/>
+      <c r="AF159" s="2" t="inlineStr"/>
+      <c r="AG159" s="2" t="inlineStr"/>
+      <c r="AH159" s="2" t="inlineStr"/>
+      <c r="AI159" s="2" t="inlineStr"/>
+      <c r="AJ159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>8d62eb3bff01441a</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>5ed7c189c90211b472ec0214d2b7901a8b9cb103b2be3f5519c68e215b46057f</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>72537</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>0.749313</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr"/>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr"/>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>0.18984163436123347</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:43.312813Z</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr"/>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr"/>
+      <c r="AB160" s="2" t="inlineStr"/>
+      <c r="AC160" s="2" t="inlineStr"/>
+      <c r="AD160" s="2" t="inlineStr"/>
+      <c r="AE160" s="2" t="inlineStr"/>
+      <c r="AF160" s="2" t="inlineStr"/>
+      <c r="AG160" s="2" t="inlineStr"/>
+      <c r="AH160" s="2" t="inlineStr"/>
+      <c r="AI160" s="2" t="inlineStr"/>
+      <c r="AJ160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>aee5d10bc3ad41e0</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>5ed7c189c90211b472ec0214d2b7901a8b9cb103b2be3f5519c68e215b46057f</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>70562</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>0.606557</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr"/>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr"/>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>0.1457275069124424</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:51.001525Z</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr"/>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr"/>
+      <c r="AB161" s="2" t="inlineStr"/>
+      <c r="AC161" s="2" t="inlineStr"/>
+      <c r="AD161" s="2" t="inlineStr"/>
+      <c r="AE161" s="2" t="inlineStr"/>
+      <c r="AF161" s="2" t="inlineStr"/>
+      <c r="AG161" s="2" t="inlineStr"/>
+      <c r="AH161" s="2" t="inlineStr"/>
+      <c r="AI161" s="2" t="inlineStr"/>
+      <c r="AJ161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>030b64fa6342495f</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>5ed7c189c90211b472ec0214d2b7901a8b9cb103b2be3f5519c68e215b46057f</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>72490</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>0.531297</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr"/>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr"/>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>0.11112893277310926</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:51.797135Z</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr"/>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr"/>
+      <c r="AB162" s="2" t="inlineStr"/>
+      <c r="AC162" s="2" t="inlineStr"/>
+      <c r="AD162" s="2" t="inlineStr"/>
+      <c r="AE162" s="2" t="inlineStr"/>
+      <c r="AF162" s="2" t="inlineStr"/>
+      <c r="AG162" s="2" t="inlineStr"/>
+      <c r="AH162" s="2" t="inlineStr"/>
+      <c r="AI162" s="2" t="inlineStr"/>
+      <c r="AJ162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>eecc8131d7364949</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>5ed7c189c90211b472ec0214d2b7901a8b9cb103b2be3f5519c68e215b46057f</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>70787</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>0.608242</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr"/>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr"/>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>0.04877063436123341</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:53.319544Z</t>
+        </is>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr"/>
+      <c r="W163" s="2" t="inlineStr"/>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr"/>
+      <c r="AB163" s="2" t="inlineStr"/>
+      <c r="AC163" s="2" t="inlineStr"/>
+      <c r="AD163" s="2" t="inlineStr"/>
+      <c r="AE163" s="2" t="inlineStr"/>
+      <c r="AF163" s="2" t="inlineStr"/>
+      <c r="AG163" s="2" t="inlineStr"/>
+      <c r="AH163" s="2" t="inlineStr"/>
+      <c r="AI163" s="2" t="inlineStr"/>
+      <c r="AJ163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>c625f3c891964b13</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>5ed7c189c90211b472ec0214d2b7901a8b9cb103b2be3f5519c68e215b46057f</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>72651</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>0.74706</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr"/>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>0.19751045045045046</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:47:00.701732Z</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr"/>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr"/>
+      <c r="AB164" s="2" t="inlineStr"/>
+      <c r="AC164" s="2" t="inlineStr"/>
+      <c r="AD164" s="2" t="inlineStr"/>
+      <c r="AE164" s="2" t="inlineStr"/>
+      <c r="AF164" s="2" t="inlineStr"/>
+      <c r="AG164" s="2" t="inlineStr"/>
+      <c r="AH164" s="2" t="inlineStr"/>
+      <c r="AI164" s="2" t="inlineStr"/>
+      <c r="AJ164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>15c54a0e44e54568</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>72533</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>0.633758</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr"/>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr"/>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>0.21358993277310928</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:11.868130Z</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr"/>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr"/>
+      <c r="AB165" s="2" t="inlineStr"/>
+      <c r="AC165" s="2" t="inlineStr"/>
+      <c r="AD165" s="2" t="inlineStr"/>
+      <c r="AE165" s="2" t="inlineStr"/>
+      <c r="AF165" s="2" t="inlineStr"/>
+      <c r="AG165" s="2" t="inlineStr"/>
+      <c r="AH165" s="2" t="inlineStr"/>
+      <c r="AI165" s="2" t="inlineStr"/>
+      <c r="AJ165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>c890aad5448d45f0</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>72534</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>0.647084</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr"/>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr"/>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>0.017454370370370453</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:13.589736Z</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr"/>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
+      <c r="AB166" s="2" t="inlineStr"/>
+      <c r="AC166" s="2" t="inlineStr"/>
+      <c r="AD166" s="2" t="inlineStr"/>
+      <c r="AE166" s="2" t="inlineStr"/>
+      <c r="AF166" s="2" t="inlineStr"/>
+      <c r="AG166" s="2" t="inlineStr"/>
+      <c r="AH166" s="2" t="inlineStr"/>
+      <c r="AI166" s="2" t="inlineStr"/>
+      <c r="AJ166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>94ccbd507c8f4dba</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>72537</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>0.748624</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr"/>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr"/>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>0.26785476923076923</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:19.555277Z</t>
+        </is>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr"/>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr"/>
+      <c r="AB167" s="2" t="inlineStr"/>
+      <c r="AC167" s="2" t="inlineStr"/>
+      <c r="AD167" s="2" t="inlineStr"/>
+      <c r="AE167" s="2" t="inlineStr"/>
+      <c r="AF167" s="2" t="inlineStr"/>
+      <c r="AG167" s="2" t="inlineStr"/>
+      <c r="AH167" s="2" t="inlineStr"/>
+      <c r="AI167" s="2" t="inlineStr"/>
+      <c r="AJ167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>9436cd14c2c349bd</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>72490</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>0.530945</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr"/>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr"/>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>0.11077693277310924</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:22.532084Z</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr"/>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr"/>
+      <c r="AB168" s="2" t="inlineStr"/>
+      <c r="AC168" s="2" t="inlineStr"/>
+      <c r="AD168" s="2" t="inlineStr"/>
+      <c r="AE168" s="2" t="inlineStr"/>
+      <c r="AF168" s="2" t="inlineStr"/>
+      <c r="AG168" s="2" t="inlineStr"/>
+      <c r="AH168" s="2" t="inlineStr"/>
+      <c r="AI168" s="2" t="inlineStr"/>
+      <c r="AJ168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>6dca5c09282c4045</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>70562</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>0.606164</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr"/>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr"/>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>0.15571354954954952</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:23.683454Z</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr"/>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr"/>
+      <c r="AB169" s="2" t="inlineStr"/>
+      <c r="AC169" s="2" t="inlineStr"/>
+      <c r="AD169" s="2" t="inlineStr"/>
+      <c r="AE169" s="2" t="inlineStr"/>
+      <c r="AF169" s="2" t="inlineStr"/>
+      <c r="AG169" s="2" t="inlineStr"/>
+      <c r="AH169" s="2" t="inlineStr"/>
+      <c r="AI169" s="2" t="inlineStr"/>
+      <c r="AJ169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>62a75c0c55c7462c</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>70787</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>0.607715</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr"/>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr"/>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>0.036899549356223194</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:26.353887Z</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr"/>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr"/>
+      <c r="AB170" s="2" t="inlineStr"/>
+      <c r="AC170" s="2" t="inlineStr"/>
+      <c r="AD170" s="2" t="inlineStr"/>
+      <c r="AE170" s="2" t="inlineStr"/>
+      <c r="AF170" s="2" t="inlineStr"/>
+      <c r="AG170" s="2" t="inlineStr"/>
+      <c r="AH170" s="2" t="inlineStr"/>
+      <c r="AI170" s="2" t="inlineStr"/>
+      <c r="AJ170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>a9a25a528d7241a3</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>72651</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>0.746375</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr"/>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr"/>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>0.14637499999999992</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:34.073375Z</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr"/>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr"/>
+      <c r="AB171" s="2" t="inlineStr"/>
+      <c r="AC171" s="2" t="inlineStr"/>
+      <c r="AD171" s="2" t="inlineStr"/>
+      <c r="AE171" s="2" t="inlineStr"/>
+      <c r="AF171" s="2" t="inlineStr"/>
+      <c r="AG171" s="2" t="inlineStr"/>
+      <c r="AH171" s="2" t="inlineStr"/>
+      <c r="AI171" s="2" t="inlineStr"/>
+      <c r="AJ171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>8b7efd7a17aa4cf8</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>72652</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>0.543196</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr"/>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr"/>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>0.0927455495495495</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:35.923759Z</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr"/>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr"/>
+      <c r="AB172" s="2" t="inlineStr"/>
+      <c r="AC172" s="2" t="inlineStr"/>
+      <c r="AD172" s="2" t="inlineStr"/>
+      <c r="AE172" s="2" t="inlineStr"/>
+      <c r="AF172" s="2" t="inlineStr"/>
+      <c r="AG172" s="2" t="inlineStr"/>
+      <c r="AH172" s="2" t="inlineStr"/>
+      <c r="AI172" s="2" t="inlineStr"/>
+      <c r="AJ172" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ152"/>
+  <autoFilter ref="A1:AJ172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ172"/>
+  <dimension ref="A1:AJ197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -14468,14 +14468,34 @@
       <c r="W135" s="2" t="inlineStr"/>
       <c r="X135" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y135" s="2" t="inlineStr"/>
-      <c r="Z135" s="2" t="inlineStr"/>
-      <c r="AA135" s="2" t="inlineStr"/>
-      <c r="AB135" s="2" t="inlineStr"/>
-      <c r="AC135" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z135" s="2" t="inlineStr">
+        <is>
+          <t>0.580000</t>
+        </is>
+      </c>
+      <c r="AA135" s="2" t="inlineStr">
+        <is>
+          <t>0.000168</t>
+        </is>
+      </c>
+      <c r="AB135" s="2" t="inlineStr">
+        <is>
+          <t>0.9058</t>
+        </is>
+      </c>
+      <c r="AC135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:55.615214Z</t>
+        </is>
+      </c>
       <c r="AD135" s="2" t="inlineStr"/>
       <c r="AE135" s="2" t="inlineStr"/>
       <c r="AF135" s="2" t="inlineStr"/>
@@ -17568,14 +17588,34 @@
       <c r="W165" s="2" t="inlineStr"/>
       <c r="X165" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y165" s="2" t="inlineStr"/>
-      <c r="Z165" s="2" t="inlineStr"/>
-      <c r="AA165" s="2" t="inlineStr"/>
-      <c r="AB165" s="2" t="inlineStr"/>
-      <c r="AC165" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z165" s="2" t="inlineStr">
+        <is>
+          <t>0.420000</t>
+        </is>
+      </c>
+      <c r="AA165" s="2" t="inlineStr">
+        <is>
+          <t>-0.000168</t>
+        </is>
+      </c>
+      <c r="AB165" s="2" t="inlineStr">
+        <is>
+          <t>2.0700</t>
+        </is>
+      </c>
+      <c r="AC165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:22.880168Z</t>
+        </is>
+      </c>
       <c r="AD165" s="2" t="inlineStr"/>
       <c r="AE165" s="2" t="inlineStr"/>
       <c r="AF165" s="2" t="inlineStr"/>
@@ -17670,14 +17710,34 @@
       <c r="W166" s="2" t="inlineStr"/>
       <c r="X166" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y166" s="2" t="inlineStr"/>
-      <c r="Z166" s="2" t="inlineStr"/>
-      <c r="AA166" s="2" t="inlineStr"/>
-      <c r="AB166" s="2" t="inlineStr"/>
-      <c r="AC166" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z166" s="2" t="inlineStr">
+        <is>
+          <t>0.630000</t>
+        </is>
+      </c>
+      <c r="AA166" s="2" t="inlineStr">
+        <is>
+          <t>0.000370</t>
+        </is>
+      </c>
+      <c r="AB166" s="2" t="inlineStr">
+        <is>
+          <t>1.0294</t>
+        </is>
+      </c>
+      <c r="AC166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:24.248877Z</t>
+        </is>
+      </c>
       <c r="AD166" s="2" t="inlineStr"/>
       <c r="AE166" s="2" t="inlineStr"/>
       <c r="AF166" s="2" t="inlineStr"/>
@@ -18298,8 +18358,2626 @@
       <c r="AI172" s="2" t="inlineStr"/>
       <c r="AJ172" s="2" t="inlineStr"/>
     </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>6d4662d618834915</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>19e41252784d7f0fb30ba60bf91a0e18dad6024caa2bc77a8c0649a56dcc9142</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>72537</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>0.74863</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr"/>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr"/>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>0.1778145493562232</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:43.266243Z</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr"/>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr"/>
+      <c r="AB173" s="2" t="inlineStr"/>
+      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AD173" s="2" t="inlineStr"/>
+      <c r="AE173" s="2" t="inlineStr"/>
+      <c r="AF173" s="2" t="inlineStr"/>
+      <c r="AG173" s="2" t="inlineStr"/>
+      <c r="AH173" s="2" t="inlineStr"/>
+      <c r="AI173" s="2" t="inlineStr"/>
+      <c r="AJ173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>d7300de9ec6f49d7</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>19e41252784d7f0fb30ba60bf91a0e18dad6024caa2bc77a8c0649a56dcc9142</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>70562</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>0.606196</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr"/>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr"/>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>0.15574554954954944</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:47.397837Z</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr"/>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr"/>
+      <c r="AB174" s="2" t="inlineStr"/>
+      <c r="AC174" s="2" t="inlineStr"/>
+      <c r="AD174" s="2" t="inlineStr"/>
+      <c r="AE174" s="2" t="inlineStr"/>
+      <c r="AF174" s="2" t="inlineStr"/>
+      <c r="AG174" s="2" t="inlineStr"/>
+      <c r="AH174" s="2" t="inlineStr"/>
+      <c r="AI174" s="2" t="inlineStr"/>
+      <c r="AJ174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>c3395adb6f984dad</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>19e41252784d7f0fb30ba60bf91a0e18dad6024caa2bc77a8c0649a56dcc9142</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>72490</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>0.530771</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr"/>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr"/>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>0.12093493442622949</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:47.938520Z</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr"/>
+      <c r="W175" s="2" t="inlineStr"/>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr"/>
+      <c r="AB175" s="2" t="inlineStr"/>
+      <c r="AC175" s="2" t="inlineStr"/>
+      <c r="AD175" s="2" t="inlineStr"/>
+      <c r="AE175" s="2" t="inlineStr"/>
+      <c r="AF175" s="2" t="inlineStr"/>
+      <c r="AG175" s="2" t="inlineStr"/>
+      <c r="AH175" s="2" t="inlineStr"/>
+      <c r="AI175" s="2" t="inlineStr"/>
+      <c r="AJ175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>69e7ab67d37340cf</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>19e41252784d7f0fb30ba60bf91a0e18dad6024caa2bc77a8c0649a56dcc9142</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>72651</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>0.746387</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr"/>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr"/>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>0.1755715493562232</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:57.350455Z</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr"/>
+      <c r="W176" s="2" t="inlineStr"/>
+      <c r="X176" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr"/>
+      <c r="AB176" s="2" t="inlineStr"/>
+      <c r="AC176" s="2" t="inlineStr"/>
+      <c r="AD176" s="2" t="inlineStr"/>
+      <c r="AE176" s="2" t="inlineStr"/>
+      <c r="AF176" s="2" t="inlineStr"/>
+      <c r="AG176" s="2" t="inlineStr"/>
+      <c r="AH176" s="2" t="inlineStr"/>
+      <c r="AI176" s="2" t="inlineStr"/>
+      <c r="AJ176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>6fed039948a6459a</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>19e41252784d7f0fb30ba60bf91a0e18dad6024caa2bc77a8c0649a56dcc9142</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>72652</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>0.542915</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr"/>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr"/>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>0.13307893442622953</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:59.598692Z</t>
+        </is>
+      </c>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr"/>
+      <c r="W177" s="2" t="inlineStr"/>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr"/>
+      <c r="Z177" s="2" t="inlineStr"/>
+      <c r="AA177" s="2" t="inlineStr"/>
+      <c r="AB177" s="2" t="inlineStr"/>
+      <c r="AC177" s="2" t="inlineStr"/>
+      <c r="AD177" s="2" t="inlineStr"/>
+      <c r="AE177" s="2" t="inlineStr"/>
+      <c r="AF177" s="2" t="inlineStr"/>
+      <c r="AG177" s="2" t="inlineStr"/>
+      <c r="AH177" s="2" t="inlineStr"/>
+      <c r="AI177" s="2" t="inlineStr"/>
+      <c r="AJ177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>28e7b3c941b44c60</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>25a966f9bdcbb0da4a43eca3b5197daad1ed61e4873cc9cdd930cb372ab02463</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>70562</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>0.605932</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr"/>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr"/>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>0.14510250691244242</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:49.309321Z</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr"/>
+      <c r="W178" s="2" t="inlineStr"/>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr"/>
+      <c r="Z178" s="2" t="inlineStr"/>
+      <c r="AA178" s="2" t="inlineStr"/>
+      <c r="AB178" s="2" t="inlineStr"/>
+      <c r="AC178" s="2" t="inlineStr"/>
+      <c r="AD178" s="2" t="inlineStr"/>
+      <c r="AE178" s="2" t="inlineStr"/>
+      <c r="AF178" s="2" t="inlineStr"/>
+      <c r="AG178" s="2" t="inlineStr"/>
+      <c r="AH178" s="2" t="inlineStr"/>
+      <c r="AI178" s="2" t="inlineStr"/>
+      <c r="AJ178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>b37e035ceca24c12</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>25a966f9bdcbb0da4a43eca3b5197daad1ed61e4873cc9cdd930cb372ab02463</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>72490</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>0.53107</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr"/>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr"/>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>0.11090193277310928</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:49.810227Z</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="2" t="inlineStr"/>
+      <c r="W179" s="2" t="inlineStr"/>
+      <c r="X179" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y179" s="2" t="inlineStr"/>
+      <c r="Z179" s="2" t="inlineStr"/>
+      <c r="AA179" s="2" t="inlineStr"/>
+      <c r="AB179" s="2" t="inlineStr"/>
+      <c r="AC179" s="2" t="inlineStr"/>
+      <c r="AD179" s="2" t="inlineStr"/>
+      <c r="AE179" s="2" t="inlineStr"/>
+      <c r="AF179" s="2" t="inlineStr"/>
+      <c r="AG179" s="2" t="inlineStr"/>
+      <c r="AH179" s="2" t="inlineStr"/>
+      <c r="AI179" s="2" t="inlineStr"/>
+      <c r="AJ179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>24716391473f4cd3</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>25a966f9bdcbb0da4a43eca3b5197daad1ed61e4873cc9cdd930cb372ab02463</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>72651</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>0.74568</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr"/>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr"/>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>0.1748645493562232</t>
+        </is>
+      </c>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:03:01.101624Z</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr"/>
+      <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="2" t="inlineStr"/>
+      <c r="W180" s="2" t="inlineStr"/>
+      <c r="X180" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y180" s="2" t="inlineStr"/>
+      <c r="Z180" s="2" t="inlineStr"/>
+      <c r="AA180" s="2" t="inlineStr"/>
+      <c r="AB180" s="2" t="inlineStr"/>
+      <c r="AC180" s="2" t="inlineStr"/>
+      <c r="AD180" s="2" t="inlineStr"/>
+      <c r="AE180" s="2" t="inlineStr"/>
+      <c r="AF180" s="2" t="inlineStr"/>
+      <c r="AG180" s="2" t="inlineStr"/>
+      <c r="AH180" s="2" t="inlineStr"/>
+      <c r="AI180" s="2" t="inlineStr"/>
+      <c r="AJ180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>1d2cd721d0054fc3</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>25a966f9bdcbb0da4a43eca3b5197daad1ed61e4873cc9cdd930cb372ab02463</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>72652</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>0.54303</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="2" t="inlineStr"/>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr"/>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>0.12286193277310925</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:03:03.176188Z</t>
+        </is>
+      </c>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="inlineStr"/>
+      <c r="V181" s="2" t="inlineStr"/>
+      <c r="W181" s="2" t="inlineStr"/>
+      <c r="X181" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y181" s="2" t="inlineStr"/>
+      <c r="Z181" s="2" t="inlineStr"/>
+      <c r="AA181" s="2" t="inlineStr"/>
+      <c r="AB181" s="2" t="inlineStr"/>
+      <c r="AC181" s="2" t="inlineStr"/>
+      <c r="AD181" s="2" t="inlineStr"/>
+      <c r="AE181" s="2" t="inlineStr"/>
+      <c r="AF181" s="2" t="inlineStr"/>
+      <c r="AG181" s="2" t="inlineStr"/>
+      <c r="AH181" s="2" t="inlineStr"/>
+      <c r="AI181" s="2" t="inlineStr"/>
+      <c r="AJ181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>cb6824ba50e44c3e</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>95c0b03a7dffafd85c27ca9ed669e331e7385a1d064329e5a50c6fe806eb56d1</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>70562</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>0.605841</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr"/>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr"/>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>0.14501150691244236</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:37.231379Z</t>
+        </is>
+      </c>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="2" t="inlineStr"/>
+      <c r="W182" s="2" t="inlineStr"/>
+      <c r="X182" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y182" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z182" s="2" t="inlineStr"/>
+      <c r="AA182" s="2" t="inlineStr"/>
+      <c r="AB182" s="2" t="inlineStr">
+        <is>
+          <t>-1.2500</t>
+        </is>
+      </c>
+      <c r="AC182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:58.683552Z</t>
+        </is>
+      </c>
+      <c r="AD182" s="2" t="inlineStr"/>
+      <c r="AE182" s="2" t="inlineStr"/>
+      <c r="AF182" s="2" t="inlineStr"/>
+      <c r="AG182" s="2" t="inlineStr"/>
+      <c r="AH182" s="2" t="inlineStr"/>
+      <c r="AI182" s="2" t="inlineStr"/>
+      <c r="AJ182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2d5f1b9d43f34266</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>95c0b03a7dffafd85c27ca9ed669e331e7385a1d064329e5a50c6fe806eb56d1</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>72490</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>0.531055</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="2" t="inlineStr"/>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr"/>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>0.11088693277310929</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:37.738828Z</t>
+        </is>
+      </c>
+      <c r="S183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr"/>
+      <c r="W183" s="2" t="inlineStr"/>
+      <c r="X183" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y183" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z183" s="2" t="inlineStr"/>
+      <c r="AA183" s="2" t="inlineStr"/>
+      <c r="AB183" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:00.386329Z</t>
+        </is>
+      </c>
+      <c r="AD183" s="2" t="inlineStr"/>
+      <c r="AE183" s="2" t="inlineStr"/>
+      <c r="AF183" s="2" t="inlineStr"/>
+      <c r="AG183" s="2" t="inlineStr"/>
+      <c r="AH183" s="2" t="inlineStr"/>
+      <c r="AI183" s="2" t="inlineStr"/>
+      <c r="AJ183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>0b99a71d8a5b48be</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>95c0b03a7dffafd85c27ca9ed669e331e7385a1d064329e5a50c6fe806eb56d1</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>72651</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>0.745356</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr"/>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr"/>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>0.1745405493562232</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:47.216028Z</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr"/>
+      <c r="W184" s="2" t="inlineStr"/>
+      <c r="X184" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y184" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z184" s="2" t="inlineStr"/>
+      <c r="AA184" s="2" t="inlineStr"/>
+      <c r="AB184" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:51.384190Z</t>
+        </is>
+      </c>
+      <c r="AD184" s="2" t="inlineStr"/>
+      <c r="AE184" s="2" t="inlineStr"/>
+      <c r="AF184" s="2" t="inlineStr"/>
+      <c r="AG184" s="2" t="inlineStr"/>
+      <c r="AH184" s="2" t="inlineStr"/>
+      <c r="AI184" s="2" t="inlineStr"/>
+      <c r="AJ184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>15af0f180650493d</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>95c0b03a7dffafd85c27ca9ed669e331e7385a1d064329e5a50c6fe806eb56d1</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>72652</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>0.543025</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr"/>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr"/>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>0.13318893442622948</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:53.654611Z</t>
+        </is>
+      </c>
+      <c r="S185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr"/>
+      <c r="W185" s="2" t="inlineStr"/>
+      <c r="X185" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y185" s="2" t="inlineStr"/>
+      <c r="Z185" s="2" t="inlineStr"/>
+      <c r="AA185" s="2" t="inlineStr"/>
+      <c r="AB185" s="2" t="inlineStr"/>
+      <c r="AC185" s="2" t="inlineStr"/>
+      <c r="AD185" s="2" t="inlineStr"/>
+      <c r="AE185" s="2" t="inlineStr"/>
+      <c r="AF185" s="2" t="inlineStr"/>
+      <c r="AG185" s="2" t="inlineStr"/>
+      <c r="AH185" s="2" t="inlineStr"/>
+      <c r="AI185" s="2" t="inlineStr"/>
+      <c r="AJ185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>e89f2164011c4f11</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>fe03335fd93db1544dba21d90e64b614b66d4504f6b07bd760b4633bb3785ef9</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>70561</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>0.672341</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr"/>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr"/>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>0.09250906722689078</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:30:28.428004Z</t>
+        </is>
+      </c>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr"/>
+      <c r="W186" s="2" t="inlineStr"/>
+      <c r="X186" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y186" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z186" s="2" t="inlineStr"/>
+      <c r="AA186" s="2" t="inlineStr"/>
+      <c r="AB186" s="2" t="inlineStr">
+        <is>
+          <t>-1.7500</t>
+        </is>
+      </c>
+      <c r="AC186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:03.246162Z</t>
+        </is>
+      </c>
+      <c r="AD186" s="2" t="inlineStr"/>
+      <c r="AE186" s="2" t="inlineStr"/>
+      <c r="AF186" s="2" t="inlineStr"/>
+      <c r="AG186" s="2" t="inlineStr"/>
+      <c r="AH186" s="2" t="inlineStr"/>
+      <c r="AI186" s="2" t="inlineStr"/>
+      <c r="AJ186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>aba136d044ee468d</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>ba62d4174c52c7a2934bcbd8b028649e6d31b496f5b9eab70ce8b6a17fb58aa6</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>72652</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>0.542916</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr"/>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="inlineStr"/>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>0.13307993442622945</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:13.521189Z</t>
+        </is>
+      </c>
+      <c r="S187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr"/>
+      <c r="W187" s="2" t="inlineStr"/>
+      <c r="X187" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y187" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z187" s="2" t="inlineStr">
+        <is>
+          <t>0.410000</t>
+        </is>
+      </c>
+      <c r="AA187" s="2" t="inlineStr">
+        <is>
+          <t>0.000164</t>
+        </is>
+      </c>
+      <c r="AB187" s="2" t="inlineStr">
+        <is>
+          <t>1.4400</t>
+        </is>
+      </c>
+      <c r="AC187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:52.824976Z</t>
+        </is>
+      </c>
+      <c r="AD187" s="2" t="inlineStr"/>
+      <c r="AE187" s="2" t="inlineStr"/>
+      <c r="AF187" s="2" t="inlineStr"/>
+      <c r="AG187" s="2" t="inlineStr"/>
+      <c r="AH187" s="2" t="inlineStr"/>
+      <c r="AI187" s="2" t="inlineStr"/>
+      <c r="AJ187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>0e01a2a4e5c84788</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>cfb18a4c5dd9cd86deb9f3f8da3e6c309d1fba85e6dd2af9e67ce04ac966ad26</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>74187</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>0.585708</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr"/>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="inlineStr"/>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
+          <t>0.18570799999999998</t>
+        </is>
+      </c>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:06:01.933250Z</t>
+        </is>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="2" t="inlineStr"/>
+      <c r="W188" s="2" t="inlineStr"/>
+      <c r="X188" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y188" s="2" t="inlineStr"/>
+      <c r="Z188" s="2" t="inlineStr"/>
+      <c r="AA188" s="2" t="inlineStr"/>
+      <c r="AB188" s="2" t="inlineStr"/>
+      <c r="AC188" s="2" t="inlineStr"/>
+      <c r="AD188" s="2" t="inlineStr"/>
+      <c r="AE188" s="2" t="inlineStr"/>
+      <c r="AF188" s="2" t="inlineStr"/>
+      <c r="AG188" s="2" t="inlineStr"/>
+      <c r="AH188" s="2" t="inlineStr"/>
+      <c r="AI188" s="2" t="inlineStr"/>
+      <c r="AJ188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>84119f17862c4d99</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>cfb18a4c5dd9cd86deb9f3f8da3e6c309d1fba85e6dd2af9e67ce04ac966ad26</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>72721</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>0.584038</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr"/>
+      <c r="N189" s="2" t="inlineStr"/>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P189" s="2" t="inlineStr"/>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>0.14350936563876648</t>
+        </is>
+      </c>
+      <c r="R189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:06:04.312835Z</t>
+        </is>
+      </c>
+      <c r="S189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="inlineStr"/>
+      <c r="U189" s="2" t="inlineStr"/>
+      <c r="V189" s="2" t="inlineStr"/>
+      <c r="W189" s="2" t="inlineStr"/>
+      <c r="X189" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y189" s="2" t="inlineStr"/>
+      <c r="Z189" s="2" t="inlineStr"/>
+      <c r="AA189" s="2" t="inlineStr"/>
+      <c r="AB189" s="2" t="inlineStr"/>
+      <c r="AC189" s="2" t="inlineStr"/>
+      <c r="AD189" s="2" t="inlineStr"/>
+      <c r="AE189" s="2" t="inlineStr"/>
+      <c r="AF189" s="2" t="inlineStr"/>
+      <c r="AG189" s="2" t="inlineStr"/>
+      <c r="AH189" s="2" t="inlineStr"/>
+      <c r="AI189" s="2" t="inlineStr"/>
+      <c r="AJ189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>1b8bbe44e780490a</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>358d57aa29e758f0c458ee789089118096199f59cf8b88918d9c205e9f5bc5fb</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>74187</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>0.585638</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr"/>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr"/>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>0.18563799999999997</t>
+        </is>
+      </c>
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:42.022133Z</t>
+        </is>
+      </c>
+      <c r="S190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="inlineStr"/>
+      <c r="U190" s="2" t="inlineStr"/>
+      <c r="V190" s="2" t="inlineStr"/>
+      <c r="W190" s="2" t="inlineStr"/>
+      <c r="X190" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y190" s="2" t="inlineStr"/>
+      <c r="Z190" s="2" t="inlineStr"/>
+      <c r="AA190" s="2" t="inlineStr"/>
+      <c r="AB190" s="2" t="inlineStr"/>
+      <c r="AC190" s="2" t="inlineStr"/>
+      <c r="AD190" s="2" t="inlineStr"/>
+      <c r="AE190" s="2" t="inlineStr"/>
+      <c r="AF190" s="2" t="inlineStr"/>
+      <c r="AG190" s="2" t="inlineStr"/>
+      <c r="AH190" s="2" t="inlineStr"/>
+      <c r="AI190" s="2" t="inlineStr"/>
+      <c r="AJ190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>3b595d279517419d</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>358d57aa29e758f0c458ee789089118096199f59cf8b88918d9c205e9f5bc5fb</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>72721</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>0.583914</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr"/>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr"/>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>0.13346354954954953</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:43.852876Z</t>
+        </is>
+      </c>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr"/>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr"/>
+      <c r="W191" s="2" t="inlineStr"/>
+      <c r="X191" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y191" s="2" t="inlineStr"/>
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr"/>
+      <c r="AB191" s="2" t="inlineStr"/>
+      <c r="AC191" s="2" t="inlineStr"/>
+      <c r="AD191" s="2" t="inlineStr"/>
+      <c r="AE191" s="2" t="inlineStr"/>
+      <c r="AF191" s="2" t="inlineStr"/>
+      <c r="AG191" s="2" t="inlineStr"/>
+      <c r="AH191" s="2" t="inlineStr"/>
+      <c r="AI191" s="2" t="inlineStr"/>
+      <c r="AJ191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>b706fc92e157492c</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>f1c53c1821e5cd5120b099293c21ae8eca632261cab4ffd9dd67a853e3ea640b</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>74184</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>0.652392</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr"/>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr"/>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>0.15239199999999997</t>
+        </is>
+      </c>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:23.012683Z</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr"/>
+      <c r="W192" s="2" t="inlineStr"/>
+      <c r="X192" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr"/>
+      <c r="AB192" s="2" t="inlineStr"/>
+      <c r="AC192" s="2" t="inlineStr"/>
+      <c r="AD192" s="2" t="inlineStr"/>
+      <c r="AE192" s="2" t="inlineStr"/>
+      <c r="AF192" s="2" t="inlineStr"/>
+      <c r="AG192" s="2" t="inlineStr"/>
+      <c r="AH192" s="2" t="inlineStr"/>
+      <c r="AI192" s="2" t="inlineStr"/>
+      <c r="AJ192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>99ae561aeece491a</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>f1c53c1821e5cd5120b099293c21ae8eca632261cab4ffd9dd67a853e3ea640b</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>74187</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>0.585253</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr"/>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="inlineStr"/>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>0.185253</t>
+        </is>
+      </c>
+      <c r="R193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:25.574031Z</t>
+        </is>
+      </c>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="inlineStr"/>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr"/>
+      <c r="W193" s="2" t="inlineStr"/>
+      <c r="X193" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
+      <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr"/>
+      <c r="AB193" s="2" t="inlineStr"/>
+      <c r="AC193" s="2" t="inlineStr"/>
+      <c r="AD193" s="2" t="inlineStr"/>
+      <c r="AE193" s="2" t="inlineStr"/>
+      <c r="AF193" s="2" t="inlineStr"/>
+      <c r="AG193" s="2" t="inlineStr"/>
+      <c r="AH193" s="2" t="inlineStr"/>
+      <c r="AI193" s="2" t="inlineStr"/>
+      <c r="AJ193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>39ddd60b108a4c09</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>f1c53c1821e5cd5120b099293c21ae8eca632261cab4ffd9dd67a853e3ea640b</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>72721</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>0.584011</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr"/>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr"/>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>0.13356054954954943</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:27.602693Z</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr"/>
+      <c r="W194" s="2" t="inlineStr"/>
+      <c r="X194" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr"/>
+      <c r="AA194" s="2" t="inlineStr"/>
+      <c r="AB194" s="2" t="inlineStr"/>
+      <c r="AC194" s="2" t="inlineStr"/>
+      <c r="AD194" s="2" t="inlineStr"/>
+      <c r="AE194" s="2" t="inlineStr"/>
+      <c r="AF194" s="2" t="inlineStr"/>
+      <c r="AG194" s="2" t="inlineStr"/>
+      <c r="AH194" s="2" t="inlineStr"/>
+      <c r="AI194" s="2" t="inlineStr"/>
+      <c r="AJ194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>486e5d04ed1746ad</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>74184</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>0.651856</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="2" t="inlineStr"/>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr"/>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>0.16165992156862746</t>
+        </is>
+      </c>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:04.782971Z</t>
+        </is>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="inlineStr"/>
+      <c r="W195" s="2" t="inlineStr"/>
+      <c r="X195" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y195" s="2" t="inlineStr"/>
+      <c r="Z195" s="2" t="inlineStr"/>
+      <c r="AA195" s="2" t="inlineStr"/>
+      <c r="AB195" s="2" t="inlineStr"/>
+      <c r="AC195" s="2" t="inlineStr"/>
+      <c r="AD195" s="2" t="inlineStr"/>
+      <c r="AE195" s="2" t="inlineStr"/>
+      <c r="AF195" s="2" t="inlineStr"/>
+      <c r="AG195" s="2" t="inlineStr"/>
+      <c r="AH195" s="2" t="inlineStr"/>
+      <c r="AI195" s="2" t="inlineStr"/>
+      <c r="AJ195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>e8f7be51ed6d4e48</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>74187</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>0.584786</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr"/>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="inlineStr"/>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>0.184786</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:06.305684Z</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="inlineStr"/>
+      <c r="V196" s="2" t="inlineStr"/>
+      <c r="W196" s="2" t="inlineStr"/>
+      <c r="X196" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y196" s="2" t="inlineStr"/>
+      <c r="Z196" s="2" t="inlineStr"/>
+      <c r="AA196" s="2" t="inlineStr"/>
+      <c r="AB196" s="2" t="inlineStr"/>
+      <c r="AC196" s="2" t="inlineStr"/>
+      <c r="AD196" s="2" t="inlineStr"/>
+      <c r="AE196" s="2" t="inlineStr"/>
+      <c r="AF196" s="2" t="inlineStr"/>
+      <c r="AG196" s="2" t="inlineStr"/>
+      <c r="AH196" s="2" t="inlineStr"/>
+      <c r="AI196" s="2" t="inlineStr"/>
+      <c r="AJ196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>3be3ad57c8084878</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>72721</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>0.584222</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="2" t="inlineStr"/>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr"/>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>0.12339250691244241</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:08.265612Z</t>
+        </is>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="inlineStr"/>
+      <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="2" t="inlineStr"/>
+      <c r="W197" s="2" t="inlineStr"/>
+      <c r="X197" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y197" s="2" t="inlineStr"/>
+      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="AA197" s="2" t="inlineStr"/>
+      <c r="AB197" s="2" t="inlineStr"/>
+      <c r="AC197" s="2" t="inlineStr"/>
+      <c r="AD197" s="2" t="inlineStr"/>
+      <c r="AE197" s="2" t="inlineStr"/>
+      <c r="AF197" s="2" t="inlineStr"/>
+      <c r="AG197" s="2" t="inlineStr"/>
+      <c r="AH197" s="2" t="inlineStr"/>
+      <c r="AI197" s="2" t="inlineStr"/>
+      <c r="AJ197" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ172"/>
+  <autoFilter ref="A1:AJ197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$198</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ197"/>
+  <dimension ref="A1:AJ198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -20756,14 +20756,34 @@
       <c r="W195" s="2" t="inlineStr"/>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y195" s="2" t="inlineStr"/>
-      <c r="Z195" s="2" t="inlineStr"/>
-      <c r="AA195" s="2" t="inlineStr"/>
-      <c r="AB195" s="2" t="inlineStr"/>
-      <c r="AC195" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y195" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z195" s="2" t="inlineStr">
+        <is>
+          <t>0.490000</t>
+        </is>
+      </c>
+      <c r="AA195" s="2" t="inlineStr">
+        <is>
+          <t>-0.000196</t>
+        </is>
+      </c>
+      <c r="AB195" s="2" t="inlineStr">
+        <is>
+          <t>1.8200</t>
+        </is>
+      </c>
+      <c r="AC195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:27.196281Z</t>
+        </is>
+      </c>
       <c r="AD195" s="2" t="inlineStr"/>
       <c r="AE195" s="2" t="inlineStr"/>
       <c r="AF195" s="2" t="inlineStr"/>
@@ -20976,8 +20996,110 @@
       <c r="AI197" s="2" t="inlineStr"/>
       <c r="AJ197" s="2" t="inlineStr"/>
     </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>d719dc12bc28449b</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>f2e7f884fc01634e12d74f8812661c5cb67e5be22fb9ba0e801020448143127e</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>72721</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>0.583902</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr"/>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr"/>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>0.183902</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:09.334825Z</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="2" t="inlineStr"/>
+      <c r="W198" s="2" t="inlineStr"/>
+      <c r="X198" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y198" s="2" t="inlineStr"/>
+      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="AA198" s="2" t="inlineStr"/>
+      <c r="AB198" s="2" t="inlineStr"/>
+      <c r="AC198" s="2" t="inlineStr"/>
+      <c r="AD198" s="2" t="inlineStr"/>
+      <c r="AE198" s="2" t="inlineStr"/>
+      <c r="AF198" s="2" t="inlineStr"/>
+      <c r="AG198" s="2" t="inlineStr"/>
+      <c r="AH198" s="2" t="inlineStr"/>
+      <c r="AI198" s="2" t="inlineStr"/>
+      <c r="AJ198" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ197"/>
+  <autoFilter ref="A1:AJ198"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>